--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\082_083\ward1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40014554-901F-4B74-B7BE-F2A6A0538C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>l;= g+=</t>
   </si>
@@ -69,9 +68,6 @@
     <t>dx+uL eQf</t>
   </si>
   <si>
-    <t>cGo eQf</t>
-  </si>
-  <si>
     <t>kf]iffs vr{</t>
   </si>
   <si>
@@ -93,9 +89,6 @@
     <t>s= ;+= sf]if ;fk6L</t>
   </si>
   <si>
-    <t xml:space="preserve">k]G;g sf]if yk </t>
-  </si>
-  <si>
     <t>hDdf s6\6L</t>
   </si>
   <si>
@@ -121,13 +114,22 @@
   </si>
   <si>
     <t>s6\6L</t>
+  </si>
+  <si>
+    <t>s/ of]Uo cfo</t>
+  </si>
+  <si>
+    <t>k]G;g sf]if yk -of]ubfgdf cfwfl/t lgj[Qe/0f tyf pkbfg sf]if_</t>
+  </si>
+  <si>
+    <t>cGo eQf -rfF8kj{ vr{_</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,13 +148,27 @@
       <color theme="1"/>
       <name val="Preeti"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -182,25 +198,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,80 +505,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="5.140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" customWidth="1"/>
-    <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="6.85546875" customWidth="1"/>
-    <col min="18" max="18" width="7.7109375" customWidth="1"/>
-    <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="7"/>
+    <col min="6" max="6" width="6.21875" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="11"/>
+    <col min="11" max="11" width="8.88671875" style="11"/>
+    <col min="13" max="13" width="7.21875" customWidth="1"/>
+    <col min="14" max="14" width="5.109375" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" style="7" customWidth="1"/>
+    <col min="16" max="16" width="8" style="11" customWidth="1"/>
+    <col min="17" max="17" width="6.88671875" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" customWidth="1"/>
+    <col min="21" max="21" width="14.44140625" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="7"/>
+    <col min="24" max="24" width="8.88671875" style="14"/>
+    <col min="27" max="27" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5" t="s">
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="AA1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AB1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" s="2" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+    </row>
+    <row r="2" spans="1:28" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -563,7 +600,7 @@
       <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -575,228 +612,704 @@
       <c r="J2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P2" s="6"/>
+      <c r="P2" s="12"/>
       <c r="Q2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="V2" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4">
+      <c r="W2" s="5"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="6">
         <v>32902</v>
       </c>
-      <c r="E3" s="4">
-        <f>D3/30*4</f>
-        <v>4386.9333333333334</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4">
+      <c r="E3" s="6">
+        <f>ROUNDUP(D3/30,0)*4</f>
+        <v>4388</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="10">
         <f>SUM(D3:F3)</f>
-        <v>37288.933333333334</v>
-      </c>
-      <c r="H3" s="4">
-        <f>11.333%*D3</f>
-        <v>3728.7836600000001</v>
-      </c>
-      <c r="I3" s="4">
+        <v>37290</v>
+      </c>
+      <c r="H3" s="2">
+        <f>10%*G3</f>
+        <v>3729</v>
+      </c>
+      <c r="I3" s="2">
         <v>400</v>
       </c>
-      <c r="J3" s="4">
-        <f>6.8%*D3</f>
-        <v>2237.3360000000002</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="J3" s="2">
+        <f>6%*G3</f>
+        <v>2237.4</v>
+      </c>
+      <c r="K3" s="10">
         <f>SUM(G3:J3)</f>
-        <v>43655.052993333338</v>
-      </c>
-      <c r="L3" s="4">
+        <v>43656.4</v>
+      </c>
+      <c r="L3" s="2">
         <v>2000</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="2">
         <v>0</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4">
+      <c r="N3" s="2"/>
+      <c r="O3" s="6">
         <f>SUM(L3:M3)</f>
         <v>2000</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="10">
         <f>K3+O3</f>
-        <v>45655.052993333338</v>
-      </c>
-      <c r="Q3" s="4">
+        <v>45656.4</v>
+      </c>
+      <c r="Q3" s="2">
         <v>800</v>
       </c>
-      <c r="R3" s="4">
+      <c r="R3" s="2">
         <f>H3*2</f>
-        <v>7457.5673200000001</v>
-      </c>
-      <c r="S3" s="4">
+        <v>7458</v>
+      </c>
+      <c r="S3" s="2">
         <v>5000</v>
       </c>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4">
+      <c r="T3" s="2"/>
+      <c r="U3" s="2">
         <f>J3*2</f>
-        <v>4474.6720000000005</v>
-      </c>
-      <c r="V3" s="4">
+        <v>4474.8</v>
+      </c>
+      <c r="V3" s="6">
         <f>SUM(Q3:U3)</f>
-        <v>17732.239320000001</v>
-      </c>
-      <c r="W3" s="4">
+        <v>17732.8</v>
+      </c>
+      <c r="W3" s="2">
+        <f>X3+U3</f>
+        <v>32398.400000000001</v>
+      </c>
+      <c r="X3" s="13">
         <f>P3-V3</f>
-        <v>27922.813673333338</v>
-      </c>
-      <c r="X3" s="4">
-        <f>IF(W3*13&gt;600000,1%*W3,0)</f>
+        <v>27923.600000000002</v>
+      </c>
+      <c r="Y3" s="2">
+        <f>IF(X3*13&gt;600000,1%*X3,0)</f>
         <v>0</v>
       </c>
-      <c r="Y3" s="4">
-        <f>W3-X3</f>
-        <v>27922.813673333338</v>
-      </c>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4">
+      <c r="Z3" s="2">
+        <f>X3-Y3</f>
+        <v>27923.600000000002</v>
+      </c>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="6">
         <v>34730</v>
       </c>
-      <c r="E4" s="4">
-        <f>D4/30*5</f>
-        <v>5788.3333333333339</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4">
+      <c r="E4" s="6">
+        <f>ROUNDUP(D4/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="10">
         <f>SUM(D4:F4)</f>
-        <v>40518.333333333336</v>
-      </c>
-      <c r="H4" s="4">
-        <f>11.333%*D4</f>
-        <v>3935.9508999999998</v>
-      </c>
-      <c r="I4" s="4">
-        <v>401</v>
-      </c>
-      <c r="J4" s="4">
-        <f>6.8%*D4</f>
-        <v>2361.6400000000003</v>
-      </c>
-      <c r="K4" s="4">
+        <v>39362</v>
+      </c>
+      <c r="H4" s="2">
+        <f>10%*G4</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I4" s="2">
+        <v>400</v>
+      </c>
+      <c r="J4" s="2">
+        <f>6%*G4</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K4" s="10">
         <f>SUM(G4:J4)</f>
-        <v>47216.924233333339</v>
-      </c>
-      <c r="L4" s="4">
+        <v>46059.92</v>
+      </c>
+      <c r="L4" s="2">
         <f>2000+3000</f>
         <v>5000</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="2">
+        <f>G4</f>
+        <v>39362</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="6">
+        <f>SUM(L4:M4)</f>
+        <v>44362</v>
+      </c>
+      <c r="P4" s="10">
+        <f>K4+O4</f>
+        <v>90421.92</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>800</v>
+      </c>
+      <c r="R4" s="2">
+        <f>H4*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S4" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2">
+        <f>J4*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V4" s="6">
+        <f>SUM(Q4:U4)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W4" s="2">
+        <f>X4+U4</f>
+        <v>76749.52</v>
+      </c>
+      <c r="X4" s="13">
+        <f>P4-V4</f>
+        <v>72026.080000000002</v>
+      </c>
+      <c r="Y4" s="2">
+        <f>IF(X4*13&gt;600000,1%*X4,0)</f>
+        <v>720.26080000000002</v>
+      </c>
+      <c r="Z4" s="2">
+        <f>X4-Y4</f>
+        <v>71305.819199999998</v>
+      </c>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="6">
+        <v>34730</v>
+      </c>
+      <c r="E5" s="6">
+        <f>ROUNDUP(D5/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="10">
+        <f>SUM(D5:F5)</f>
+        <v>39362</v>
+      </c>
+      <c r="H5" s="2">
+        <f>10%*G5</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I5" s="2">
+        <v>400</v>
+      </c>
+      <c r="J5" s="2">
+        <f>6%*G5</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K5" s="10">
+        <f>SUM(G5:J5)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L5" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M5" s="2">
         <v>0</v>
       </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4">
-        <f>SUM(L4:M4)</f>
+      <c r="N5" s="2"/>
+      <c r="O5" s="6">
+        <f>SUM(L5:M5)</f>
         <v>5000</v>
       </c>
-      <c r="P4" s="4">
-        <f>K4+O4</f>
-        <v>52216.924233333339</v>
-      </c>
-      <c r="Q4" s="4">
+      <c r="P5" s="10">
+        <f>K5+O5</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q5" s="2">
         <v>801</v>
       </c>
-      <c r="R4" s="4">
-        <f>H4*2</f>
-        <v>7871.9017999999996</v>
-      </c>
-      <c r="S4" s="4">
-        <v>5001</v>
-      </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4">
-        <f>J4*2</f>
-        <v>4723.2800000000007</v>
-      </c>
-      <c r="V4" s="4">
-        <f>SUM(Q4:U4)</f>
-        <v>18397.181799999998</v>
-      </c>
-      <c r="W4" s="4">
-        <f>P4-V4</f>
-        <v>33819.74243333334</v>
-      </c>
-      <c r="X4" s="4">
-        <f>IF(W4*13&gt;600000,1%*W4,0)</f>
+      <c r="R5" s="2">
+        <f>H5*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2">
+        <f>J5*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V5" s="6">
+        <f>SUM(Q5:U5)</f>
+        <v>18396.84</v>
+      </c>
+      <c r="W5" s="2">
+        <f>X5+U5</f>
+        <v>37386.519999999997</v>
+      </c>
+      <c r="X5" s="13">
+        <f>P5-V5</f>
+        <v>32663.079999999998</v>
+      </c>
+      <c r="Y5" s="2">
+        <f>IF(X5*13&gt;600000,1%*X5,0)</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="4">
-        <f>W4-X4</f>
-        <v>33819.74243333334</v>
-      </c>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="J5">
-        <f>2237/32902</f>
-        <v>6.7989787854841652E-2</v>
-      </c>
+      <c r="Z5" s="2">
+        <f>X5-Y5</f>
+        <v>32663.079999999998</v>
+      </c>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="6">
+        <v>43689</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="10">
+        <f>SUM(D6:F6)</f>
+        <v>43689</v>
+      </c>
+      <c r="H6" s="2">
+        <f>10%*G6</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I6" s="2">
+        <v>400</v>
+      </c>
+      <c r="J6" s="2">
+        <f>6%*G6</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K6" s="10">
+        <f>SUM(G6:J6)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L6" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="6">
+        <f>SUM(L6:M6)</f>
+        <v>5000</v>
+      </c>
+      <c r="P6" s="10">
+        <f>K6+O6</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>801</v>
+      </c>
+      <c r="R6" s="2">
+        <f>H6*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2">
+        <f>J6*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V6" s="6">
+        <f>SUM(Q6:U6)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="W6" s="2">
+        <f>X6+U6</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="X6" s="13">
+        <f>P6-V6</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Y6" s="2">
+        <f>IF(X6*13&gt;600000,1%*X6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
+        <f>X6-Y6</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="Q1:V1"/>
+  <mergeCells count="14">
     <mergeCell ref="W1:W2"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="D1:K1"/>
+    <mergeCell ref="AB1:AB2"/>
     <mergeCell ref="L1:O1"/>
     <mergeCell ref="P1:P2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AA2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\082_083\ward1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D324B80-E6C5-40BB-8BA0-568CC1F90A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,6 +33,88 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{AD28CD2A-6F95-4BA7-BF55-9966A86999EB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+bhadra</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{9336CFC1-3459-4BF8-B3A8-5B5478745621}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Ashwin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{8713AFB4-3DF0-432A-8F9E-0D0B99DA63F9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Kartik</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
@@ -128,8 +211,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +238,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -205,12 +301,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -221,11 +311,17 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,92 +601,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="5" width="8.88671875" style="7"/>
-    <col min="6" max="6" width="6.21875" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="11"/>
-    <col min="11" max="11" width="8.88671875" style="11"/>
-    <col min="13" max="13" width="7.21875" customWidth="1"/>
-    <col min="14" max="14" width="5.109375" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="8" style="11" customWidth="1"/>
-    <col min="17" max="17" width="6.88671875" customWidth="1"/>
-    <col min="18" max="18" width="7.6640625" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" customWidth="1"/>
-    <col min="21" max="21" width="14.44140625" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="7"/>
-    <col min="24" max="24" width="8.88671875" style="14"/>
-    <col min="27" max="27" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="5"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="9"/>
+    <col min="11" max="11" width="8.85546875" style="9"/>
+    <col min="13" max="13" width="7.28515625" customWidth="1"/>
+    <col min="14" max="14" width="5.140625" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="8" style="9" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" customWidth="1"/>
+    <col min="18" max="18" width="7.7109375" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="5"/>
+    <col min="24" max="24" width="8.85546875" style="11"/>
+    <col min="27" max="27" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4" t="s">
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="12" t="s">
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="5" t="s">
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="X1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="12" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+    <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -600,7 +696,7 @@
       <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -612,7 +708,7 @@
       <c r="J2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="7" t="s">
         <v>6</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -627,7 +723,7 @@
       <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="12"/>
+      <c r="P2" s="14"/>
       <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
@@ -646,26 +742,26 @@
       <c r="V2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="5"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="W2" s="12"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>32902</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="4">
         <f>ROUNDUP(D3/30,0)*4</f>
         <v>4388</v>
       </c>
       <c r="F3" s="2"/>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <f>SUM(D3:F3)</f>
         <v>37290</v>
       </c>
@@ -680,7 +776,7 @@
         <f>6%*G3</f>
         <v>2237.4</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="8">
         <f>SUM(G3:J3)</f>
         <v>43656.4</v>
       </c>
@@ -691,11 +787,11 @@
         <v>0</v>
       </c>
       <c r="N3" s="2"/>
-      <c r="O3" s="6">
+      <c r="O3" s="4">
         <f>SUM(L3:M3)</f>
         <v>2000</v>
       </c>
-      <c r="P3" s="10">
+      <c r="P3" s="8">
         <f>K3+O3</f>
         <v>45656.4</v>
       </c>
@@ -714,7 +810,7 @@
         <f>J3*2</f>
         <v>4474.8</v>
       </c>
-      <c r="V3" s="6">
+      <c r="V3" s="4">
         <f>SUM(Q3:U3)</f>
         <v>17732.8</v>
       </c>
@@ -722,7 +818,7 @@
         <f>X3+U3</f>
         <v>32398.400000000001</v>
       </c>
-      <c r="X3" s="13">
+      <c r="X3" s="10">
         <f>P3-V3</f>
         <v>27923.600000000002</v>
       </c>
@@ -737,19 +833,19 @@
       <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>34730</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <f>ROUNDUP(D4/30,0)*4</f>
         <v>4632</v>
       </c>
       <c r="F4" s="2"/>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <f>SUM(D4:F4)</f>
         <v>39362</v>
       </c>
@@ -764,7 +860,7 @@
         <f>6%*G4</f>
         <v>2361.7199999999998</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="8">
         <f>SUM(G4:J4)</f>
         <v>46059.92</v>
       </c>
@@ -777,11 +873,11 @@
         <v>39362</v>
       </c>
       <c r="N4" s="2"/>
-      <c r="O4" s="6">
+      <c r="O4" s="4">
         <f>SUM(L4:M4)</f>
         <v>44362</v>
       </c>
-      <c r="P4" s="10">
+      <c r="P4" s="8">
         <f>K4+O4</f>
         <v>90421.92</v>
       </c>
@@ -800,7 +896,7 @@
         <f>J4*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V4" s="6">
+      <c r="V4" s="4">
         <f>SUM(Q4:U4)</f>
         <v>18395.84</v>
       </c>
@@ -808,7 +904,7 @@
         <f>X4+U4</f>
         <v>76749.52</v>
       </c>
-      <c r="X4" s="13">
+      <c r="X4" s="10">
         <f>P4-V4</f>
         <v>72026.080000000002</v>
       </c>
@@ -823,19 +919,19 @@
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>34730</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <f>ROUNDUP(D5/30,0)*4</f>
         <v>4632</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <f>SUM(D5:F5)</f>
         <v>39362</v>
       </c>
@@ -850,7 +946,7 @@
         <f>6%*G5</f>
         <v>2361.7199999999998</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="8">
         <f>SUM(G5:J5)</f>
         <v>46059.92</v>
       </c>
@@ -862,16 +958,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="2"/>
-      <c r="O5" s="6">
+      <c r="O5" s="4">
         <f>SUM(L5:M5)</f>
         <v>5000</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="8">
         <f>K5+O5</f>
         <v>51059.92</v>
       </c>
       <c r="Q5" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R5" s="2">
         <f>H5*2</f>
@@ -885,17 +981,17 @@
         <f>J5*2</f>
         <v>4723.4399999999996</v>
       </c>
-      <c r="V5" s="6">
+      <c r="V5" s="4">
         <f>SUM(Q5:U5)</f>
-        <v>18396.84</v>
+        <v>18395.84</v>
       </c>
       <c r="W5" s="2">
         <f>X5+U5</f>
-        <v>37386.519999999997</v>
-      </c>
-      <c r="X5" s="13">
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X5" s="10">
         <f>P5-V5</f>
-        <v>32663.079999999998</v>
+        <v>32664.079999999998</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(X5*13&gt;600000,1%*X5,0)</f>
@@ -903,40 +999,41 @@
       </c>
       <c r="Z5" s="2">
         <f>X5-Y5</f>
-        <v>32663.079999999998</v>
+        <v>32664.079999999998</v>
       </c>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="6">
-        <v>43689</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
+      <c r="D6" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E6" s="4">
+        <f>ROUNDUP(D6/30,0)*4</f>
+        <v>4632</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="10">
+      <c r="G6" s="8">
         <f>SUM(D6:F6)</f>
-        <v>43689</v>
+        <v>39362</v>
       </c>
       <c r="H6" s="2">
         <f>10%*G6</f>
-        <v>4368.9000000000005</v>
+        <v>3936.2000000000003</v>
       </c>
       <c r="I6" s="2">
         <v>400</v>
       </c>
       <c r="J6" s="2">
         <f>6%*G6</f>
-        <v>2621.3399999999997</v>
-      </c>
-      <c r="K6" s="10">
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K6" s="8">
         <f>SUM(G6:J6)</f>
-        <v>51079.24</v>
+        <v>46059.92</v>
       </c>
       <c r="L6" s="2">
         <f>2000+3000</f>
@@ -946,40 +1043,40 @@
         <v>0</v>
       </c>
       <c r="N6" s="2"/>
-      <c r="O6" s="6">
+      <c r="O6" s="4">
         <f>SUM(L6:M6)</f>
         <v>5000</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="8">
         <f>K6+O6</f>
-        <v>56079.24</v>
+        <v>51059.92</v>
       </c>
       <c r="Q6" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R6" s="2">
         <f>H6*2</f>
-        <v>8737.8000000000011</v>
+        <v>7872.4000000000005</v>
       </c>
       <c r="S6" s="2">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2">
         <f>J6*2</f>
-        <v>5242.6799999999994</v>
-      </c>
-      <c r="V6" s="6">
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V6" s="4">
         <f>SUM(Q6:U6)</f>
-        <v>15781.48</v>
+        <v>18395.84</v>
       </c>
       <c r="W6" s="2">
         <f>X6+U6</f>
-        <v>45540.439999999995</v>
-      </c>
-      <c r="X6" s="13">
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X6" s="10">
         <f>P6-V6</f>
-        <v>40297.759999999995</v>
+        <v>32664.079999999998</v>
       </c>
       <c r="Y6" s="2">
         <f>IF(X6*13&gt;600000,1%*X6,0)</f>
@@ -987,310 +1084,454 @@
       </c>
       <c r="Z6" s="2">
         <f>X6-Y6</f>
-        <v>40297.759999999995</v>
+        <v>32664.079999999998</v>
       </c>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="10"/>
+      <c r="G7" s="8"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="10"/>
+      <c r="K7" s="8"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="10"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="8"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
-      <c r="V7" s="6"/>
+      <c r="V7" s="4"/>
       <c r="W7" s="2"/>
-      <c r="X7" s="13"/>
+      <c r="X7" s="10"/>
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="10"/>
+      <c r="G8" s="8"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="10"/>
+      <c r="K8" s="8"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="10"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="8"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="6"/>
+      <c r="V8" s="4"/>
       <c r="W8" s="2"/>
-      <c r="X8" s="13"/>
+      <c r="X8" s="10"/>
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="D9" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="G9" s="8">
+        <f>SUM(D9:F9)</f>
+        <v>43689</v>
+      </c>
+      <c r="H9" s="2">
+        <f>10%*G9</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I9" s="2">
+        <v>400</v>
+      </c>
+      <c r="J9" s="2">
+        <f>6%*G9</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K9" s="8">
+        <f>SUM(G9:J9)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L9" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
       <c r="N9" s="2"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+      <c r="O9" s="4">
+        <f>SUM(L9:M9)</f>
+        <v>5000</v>
+      </c>
+      <c r="P9" s="8">
+        <f>K9+O9</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>801</v>
+      </c>
+      <c r="R9" s="2">
+        <f>H9*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S9" s="2">
+        <v>1000</v>
+      </c>
       <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
+      <c r="U9" s="2">
+        <f>J9*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V9" s="4">
+        <f>SUM(Q9:U9)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="W9" s="2">
+        <f>X9+U9</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="X9" s="10">
+        <f>P9-V9</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Y9" s="2">
+        <f>IF(X9*13&gt;600000,1%*X9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2">
+        <f>X9-Y9</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="10"/>
+      <c r="G10" s="8"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="10"/>
+      <c r="K10" s="8"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="10"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="8"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
-      <c r="V10" s="6"/>
+      <c r="V10" s="4"/>
       <c r="W10" s="2"/>
-      <c r="X10" s="13"/>
+      <c r="X10" s="10"/>
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="10"/>
+      <c r="G11" s="8"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="10"/>
+      <c r="K11" s="8"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="10"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="8"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
-      <c r="V11" s="6"/>
+      <c r="V11" s="4"/>
       <c r="W11" s="2"/>
-      <c r="X11" s="13"/>
+      <c r="X11" s="10"/>
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="10"/>
+      <c r="G12" s="8"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="10"/>
+      <c r="K12" s="8"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="10"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="8"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
-      <c r="V12" s="6"/>
+      <c r="V12" s="4"/>
       <c r="W12" s="2"/>
-      <c r="X12" s="13"/>
+      <c r="X12" s="10"/>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="10"/>
+      <c r="G13" s="8"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="10"/>
+      <c r="K13" s="8"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="10"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="8"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
-      <c r="V13" s="6"/>
+      <c r="V13" s="4"/>
       <c r="W13" s="2"/>
-      <c r="X13" s="13"/>
+      <c r="X13" s="10"/>
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="10"/>
+      <c r="G14" s="8"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="10"/>
+      <c r="K14" s="8"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="10"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="8"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
-      <c r="V14" s="6"/>
+      <c r="V14" s="4"/>
       <c r="W14" s="2"/>
-      <c r="X14" s="13"/>
+      <c r="X14" s="10"/>
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="10"/>
+      <c r="G15" s="8"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="10"/>
+      <c r="K15" s="8"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="10"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="8"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="6"/>
+      <c r="V15" s="4"/>
       <c r="W15" s="2"/>
-      <c r="X15" s="13"/>
+      <c r="X15" s="10"/>
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="10"/>
+      <c r="G16" s="8"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="10"/>
+      <c r="K16" s="8"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="10"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="8"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
-      <c r="V16" s="6"/>
+      <c r="V16" s="4"/>
       <c r="W16" s="2"/>
-      <c r="X16" s="13"/>
+      <c r="X16" s="10"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1311,5 +1552,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D324B80-E6C5-40BB-8BA0-568CC1F90A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA314E9E-2DE7-4550-8C33-A289610C30DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,6 +108,30 @@
           </rPr>
           <t xml:space="preserve">
 Kartik</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{B599E665-7579-4A84-B571-B267676937E2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Mangsir</t>
         </r>
       </text>
     </comment>
@@ -1093,29 +1117,84 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="D7" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E7" s="4">
+        <f>ROUNDUP(D7/30,0)*4</f>
+        <v>4632</v>
+      </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="G7" s="8">
+        <f>SUM(D7:F7)</f>
+        <v>39362</v>
+      </c>
+      <c r="H7" s="2">
+        <f>10%*G7</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I7" s="2">
+        <v>400</v>
+      </c>
+      <c r="J7" s="2">
+        <f>6%*G7</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K7" s="8">
+        <f>SUM(G7:J7)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L7" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
       <c r="N7" s="2"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="O7" s="4">
+        <f>SUM(L7:M7)</f>
+        <v>5000</v>
+      </c>
+      <c r="P7" s="8">
+        <f>K7+O7</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>800</v>
+      </c>
+      <c r="R7" s="2">
+        <f>H7*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S7" s="2">
+        <v>5000</v>
+      </c>
       <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
+      <c r="U7" s="2">
+        <f>J7*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V7" s="4">
+        <f>SUM(Q7:U7)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W7" s="2">
+        <f>X7+U7</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X7" s="10">
+        <f>P7-V7</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y7" s="2">
+        <f>IF(X7*13&gt;600000,1%*X7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
+        <f>X7-Y7</f>
+        <v>32664.079999999998</v>
+      </c>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
     </row>

--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA314E9E-2DE7-4550-8C33-A289610C30DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F1D3E-A415-450B-B437-48686E68F5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -135,6 +135,72 @@
         </r>
       </text>
     </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{87073B8F-9072-4EF6-B208-947AACA7D7EC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+poush</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{5E7E19E1-C15B-4922-ACAF-F55EACE46A00}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Magh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{DFCBDEA9-2C22-4E5E-9B42-6533BB080AF6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+falgun</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -236,7 +302,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +341,17 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
     </font>
   </fonts>
   <fills count="3">
@@ -626,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -1202,29 +1279,84 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="D8" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" ref="E8:E10" si="0">ROUNDUP(D8/30,0)*4</f>
+        <v>4632</v>
+      </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="G8" s="8">
+        <f t="shared" ref="G8:G10" si="1">SUM(D8:F8)</f>
+        <v>39362</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" ref="H8:H10" si="2">10%*G8</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I8" s="2">
+        <v>400</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" ref="J8:J10" si="3">6%*G8</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" ref="K8:K10" si="4">SUM(G8:J8)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L8" s="2">
+        <f t="shared" ref="L8:L10" si="5">2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
       <c r="N8" s="2"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+      <c r="O8" s="4">
+        <f t="shared" ref="O8:O10" si="6">SUM(L8:M8)</f>
+        <v>5000</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" ref="P8:P10" si="7">K8+O8</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>800</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" ref="R8:R10" si="8">H8*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S8" s="2">
+        <v>5000</v>
+      </c>
       <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="4"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
+      <c r="U8" s="2">
+        <f t="shared" ref="U8:U10" si="9">J8*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V8" s="4">
+        <f t="shared" ref="V8:V10" si="10">SUM(Q8:U8)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W8" s="2">
+        <f t="shared" ref="W8:W10" si="11">X8+U8</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X8" s="10">
+        <f t="shared" ref="X8:X10" si="12">P8-V8</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y8" s="2">
+        <f t="shared" ref="Y8:Y10" si="13">IF(X8*13&gt;600000,1%*X8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <f t="shared" ref="Z8:Z10" si="14">X8-Y8</f>
+        <v>32664.079999999998</v>
+      </c>
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
@@ -1233,33 +1365,34 @@
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="4">
-        <v>43689</v>
+        <v>34730</v>
       </c>
       <c r="E9" s="4">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>4632</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="8">
-        <f>SUM(D9:F9)</f>
-        <v>43689</v>
+        <f t="shared" si="1"/>
+        <v>39362</v>
       </c>
       <c r="H9" s="2">
-        <f>10%*G9</f>
-        <v>4368.9000000000005</v>
+        <f t="shared" si="2"/>
+        <v>3936.2000000000003</v>
       </c>
       <c r="I9" s="2">
         <v>400</v>
       </c>
       <c r="J9" s="2">
-        <f>6%*G9</f>
-        <v>2621.3399999999997</v>
+        <f t="shared" si="3"/>
+        <v>2361.7199999999998</v>
       </c>
       <c r="K9" s="8">
-        <f>SUM(G9:J9)</f>
-        <v>51079.24</v>
+        <f t="shared" si="4"/>
+        <v>46059.92</v>
       </c>
       <c r="L9" s="2">
-        <f>2000+3000</f>
+        <f t="shared" si="5"/>
         <v>5000</v>
       </c>
       <c r="M9" s="2">
@@ -1267,47 +1400,47 @@
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="4">
-        <f>SUM(L9:M9)</f>
+        <f t="shared" si="6"/>
         <v>5000</v>
       </c>
       <c r="P9" s="8">
-        <f>K9+O9</f>
-        <v>56079.24</v>
+        <f t="shared" si="7"/>
+        <v>51059.92</v>
       </c>
       <c r="Q9" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R9" s="2">
-        <f>H9*2</f>
-        <v>8737.8000000000011</v>
+        <f t="shared" si="8"/>
+        <v>7872.4000000000005</v>
       </c>
       <c r="S9" s="2">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2">
-        <f>J9*2</f>
-        <v>5242.6799999999994</v>
+        <f t="shared" si="9"/>
+        <v>4723.4399999999996</v>
       </c>
       <c r="V9" s="4">
-        <f>SUM(Q9:U9)</f>
-        <v>15781.48</v>
+        <f t="shared" si="10"/>
+        <v>18395.84</v>
       </c>
       <c r="W9" s="2">
-        <f>X9+U9</f>
-        <v>45540.439999999995</v>
+        <f t="shared" si="11"/>
+        <v>37387.519999999997</v>
       </c>
       <c r="X9" s="10">
-        <f>P9-V9</f>
-        <v>40297.759999999995</v>
+        <f t="shared" si="12"/>
+        <v>32664.079999999998</v>
       </c>
       <c r="Y9" s="2">
-        <f>IF(X9*13&gt;600000,1%*X9,0)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Z9" s="2">
-        <f>X9-Y9</f>
-        <v>40297.759999999995</v>
+        <f t="shared" si="14"/>
+        <v>32664.079999999998</v>
       </c>
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
@@ -1316,29 +1449,84 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="D10" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>4632</v>
+      </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="G10" s="8">
+        <f t="shared" si="1"/>
+        <v>39362</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I10" s="2">
+        <v>400</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="3"/>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="4"/>
+        <v>46059.92</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
       <c r="N10" s="2"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+      <c r="O10" s="4">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" si="7"/>
+        <v>51059.92</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>800</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="8"/>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S10" s="2">
+        <v>5000</v>
+      </c>
       <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2"/>
+      <c r="U10" s="2">
+        <f t="shared" si="9"/>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V10" s="4">
+        <f t="shared" si="10"/>
+        <v>18395.84</v>
+      </c>
+      <c r="W10" s="2">
+        <f t="shared" si="11"/>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X10" s="10">
+        <f t="shared" si="12"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y10" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2">
+        <f t="shared" si="14"/>
+        <v>32664.079999999998</v>
+      </c>
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
     </row>
@@ -1376,29 +1564,83 @@
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
+      <c r="D12" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="G12" s="8">
+        <f>SUM(D12:F12)</f>
+        <v>43689</v>
+      </c>
+      <c r="H12" s="2">
+        <f>10%*G12</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I12" s="2">
+        <v>400</v>
+      </c>
+      <c r="J12" s="2">
+        <f>6%*G12</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K12" s="8">
+        <f>SUM(G12:J12)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L12" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
+      <c r="O12" s="4">
+        <f>SUM(L12:M12)</f>
+        <v>5000</v>
+      </c>
+      <c r="P12" s="8">
+        <f>K12+O12</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>801</v>
+      </c>
+      <c r="R12" s="2">
+        <f>H12*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S12" s="2">
+        <v>1000</v>
+      </c>
       <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
+      <c r="U12" s="2">
+        <f>J12*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V12" s="4">
+        <f>SUM(Q12:U12)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="W12" s="2">
+        <f>X12+U12</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="X12" s="10">
+        <f>P12-V12</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Y12" s="2">
+        <f>IF(X12*13&gt;600000,1%*X12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <f>X12-Y12</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
     </row>
@@ -1612,6 +1854,96 @@
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
     </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="W1:W2"/>

--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82F1D3E-A415-450B-B437-48686E68F5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8FB979-6E37-4509-AC1A-24150444DD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,6 +198,54 @@
           </rPr>
           <t xml:space="preserve">
 falgun</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{378A8198-0773-4DBB-81FF-3C343652B837}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+chaitra</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{A419E87C-F262-442D-8355-622B62EF3E47}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Baisakh</t>
         </r>
       </text>
     </comment>
@@ -703,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -714,7 +762,7 @@
     <col min="7" max="7" width="8.85546875" style="9"/>
     <col min="11" max="11" width="8.85546875" style="9"/>
     <col min="13" max="13" width="7.28515625" customWidth="1"/>
-    <col min="14" max="14" width="5.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" customWidth="1"/>
     <col min="15" max="15" width="8.5703125" style="5" customWidth="1"/>
     <col min="16" max="16" width="8" style="9" customWidth="1"/>
     <col min="17" max="17" width="6.85546875" customWidth="1"/>
@@ -1307,7 +1355,7 @@
         <v>46059.92</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" ref="L8:L10" si="5">2000+3000</f>
+        <f t="shared" ref="L8:L12" si="5">2000+3000</f>
         <v>5000</v>
       </c>
       <c r="M8" s="2">
@@ -1534,29 +1582,86 @@
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="D11" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" ref="E11:E12" si="15">ROUNDUP(D11/30,0)*4</f>
+        <v>4632</v>
+      </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
+      <c r="G11" s="8">
+        <f t="shared" ref="G11:G12" si="16">SUM(D11:F11)</f>
+        <v>39362</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" ref="H11:H12" si="17">10%*G11</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I11" s="2">
+        <v>400</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" ref="J11:J12" si="18">6%*G11</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" ref="K11:K12" si="19">SUM(G11:J11)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L11" s="2">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O11" s="4">
+        <f>SUM(L11:N11)</f>
+        <v>15000</v>
+      </c>
+      <c r="P11" s="8">
+        <f t="shared" ref="P11:P12" si="20">K11+O11</f>
+        <v>61059.92</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>800</v>
+      </c>
+      <c r="R11" s="2">
+        <f t="shared" ref="R11:R12" si="21">H11*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S11" s="2">
+        <v>5000</v>
+      </c>
       <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
+      <c r="U11" s="2">
+        <f t="shared" ref="U11:U12" si="22">J11*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V11" s="4">
+        <f t="shared" ref="V11:V12" si="23">SUM(Q11:U11)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W11" s="2">
+        <f t="shared" ref="W11:W12" si="24">X11+U11</f>
+        <v>47387.520000000004</v>
+      </c>
+      <c r="X11" s="10">
+        <f t="shared" ref="X11:X12" si="25">P11-V11</f>
+        <v>42664.08</v>
+      </c>
+      <c r="Y11" s="2">
+        <f t="shared" ref="Y11:Y12" si="26">IF(X11*13&gt;600000,1%*X11,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2">
+        <f t="shared" ref="Z11:Z12" si="27">X11-Y11</f>
+        <v>42664.08</v>
+      </c>
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
     </row>
@@ -1565,33 +1670,34 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="4">
-        <v>43689</v>
+        <v>34730</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>4632</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="8">
-        <f>SUM(D12:F12)</f>
-        <v>43689</v>
+        <f t="shared" si="16"/>
+        <v>39362</v>
       </c>
       <c r="H12" s="2">
-        <f>10%*G12</f>
-        <v>4368.9000000000005</v>
+        <f t="shared" si="17"/>
+        <v>3936.2000000000003</v>
       </c>
       <c r="I12" s="2">
         <v>400</v>
       </c>
       <c r="J12" s="2">
-        <f>6%*G12</f>
-        <v>2621.3399999999997</v>
+        <f t="shared" si="18"/>
+        <v>2361.7199999999998</v>
       </c>
       <c r="K12" s="8">
-        <f>SUM(G12:J12)</f>
-        <v>51079.24</v>
+        <f t="shared" si="19"/>
+        <v>46059.92</v>
       </c>
       <c r="L12" s="2">
-        <f>2000+3000</f>
+        <f t="shared" si="5"/>
         <v>5000</v>
       </c>
       <c r="M12" s="2">
@@ -1599,47 +1705,47 @@
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="4">
-        <f>SUM(L12:M12)</f>
+        <f t="shared" ref="O11:O12" si="28">SUM(L12:M12)</f>
         <v>5000</v>
       </c>
       <c r="P12" s="8">
-        <f>K12+O12</f>
-        <v>56079.24</v>
+        <f t="shared" si="20"/>
+        <v>51059.92</v>
       </c>
       <c r="Q12" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R12" s="2">
-        <f>H12*2</f>
-        <v>8737.8000000000011</v>
+        <f t="shared" si="21"/>
+        <v>7872.4000000000005</v>
       </c>
       <c r="S12" s="2">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2">
-        <f>J12*2</f>
-        <v>5242.6799999999994</v>
+        <f t="shared" si="22"/>
+        <v>4723.4399999999996</v>
       </c>
       <c r="V12" s="4">
-        <f>SUM(Q12:U12)</f>
-        <v>15781.48</v>
+        <f t="shared" si="23"/>
+        <v>18395.84</v>
       </c>
       <c r="W12" s="2">
-        <f>X12+U12</f>
-        <v>45540.439999999995</v>
+        <f t="shared" si="24"/>
+        <v>37387.519999999997</v>
       </c>
       <c r="X12" s="10">
-        <f>P12-V12</f>
-        <v>40297.759999999995</v>
+        <f t="shared" si="25"/>
+        <v>32664.079999999998</v>
       </c>
       <c r="Y12" s="2">
-        <f>IF(X12*13&gt;600000,1%*X12,0)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="Z12" s="2">
-        <f>X12-Y12</f>
-        <v>40297.759999999995</v>
+        <f t="shared" si="27"/>
+        <v>32664.079999999998</v>
       </c>
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
@@ -1678,29 +1784,83 @@
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="D14" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="G14" s="8">
+        <f>SUM(D14:F14)</f>
+        <v>43689</v>
+      </c>
+      <c r="H14" s="2">
+        <f>10%*G14</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I14" s="2">
+        <v>400</v>
+      </c>
+      <c r="J14" s="2">
+        <f>6%*G14</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K14" s="8">
+        <f>SUM(G14:J14)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L14" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
       <c r="N14" s="2"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="O14" s="4">
+        <f>SUM(L14:M14)</f>
+        <v>5000</v>
+      </c>
+      <c r="P14" s="8">
+        <f>K14+O14</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>801</v>
+      </c>
+      <c r="R14" s="2">
+        <f>H14*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S14" s="2">
+        <v>1000</v>
+      </c>
       <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
+      <c r="U14" s="2">
+        <f>J14*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V14" s="4">
+        <f>SUM(Q14:U14)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="W14" s="2">
+        <f>X14+U14</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="X14" s="10">
+        <f>P14-V14</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Y14" s="2">
+        <f>IF(X14*13&gt;600000,1%*X14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2">
+        <f>X14-Y14</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
     </row>
@@ -1944,6 +2104,66 @@
       <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
     </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="W1:W2"/>

--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\082_083\ward1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8FB979-6E37-4509-AC1A-24150444DD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,12 +33,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>User</author>
+    <author>DELL</author>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{AD28CD2A-6F95-4BA7-BF55-9966A86999EB}">
+    <comment ref="D4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{9336CFC1-3459-4BF8-B3A8-5B5478745621}">
+    <comment ref="D5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{8713AFB4-3DF0-432A-8F9E-0D0B99DA63F9}">
+    <comment ref="D6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -111,7 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{B599E665-7579-4A84-B571-B267676937E2}">
+    <comment ref="D7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{87073B8F-9072-4EF6-B208-947AACA7D7EC}">
+    <comment ref="D8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{5E7E19E1-C15B-4922-ACAF-F55EACE46A00}">
+    <comment ref="D9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -179,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{DFCBDEA9-2C22-4E5E-9B42-6533BB080AF6}">
+    <comment ref="D10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -201,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{378A8198-0773-4DBB-81FF-3C343652B837}">
+    <comment ref="D11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -225,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{A419E87C-F262-442D-8355-622B62EF3E47}">
+    <comment ref="D12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -249,6 +249,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="D15" authorId="1" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>DELL:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+From shrawan</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -349,7 +373,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -750,31 +774,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="5" width="8.85546875" style="5"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="9"/>
-    <col min="11" max="11" width="8.85546875" style="9"/>
-    <col min="13" max="13" width="7.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="5" width="8.88671875" style="5"/>
+    <col min="6" max="6" width="6.33203125" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="9"/>
+    <col min="11" max="11" width="8.88671875" style="9"/>
+    <col min="13" max="13" width="7.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" style="5" customWidth="1"/>
     <col min="16" max="16" width="8" style="9" customWidth="1"/>
-    <col min="17" max="17" width="6.85546875" customWidth="1"/>
-    <col min="18" max="18" width="7.7109375" customWidth="1"/>
-    <col min="20" max="20" width="8.85546875" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" customWidth="1"/>
-    <col min="22" max="22" width="8.85546875" style="5"/>
-    <col min="24" max="24" width="8.85546875" style="11"/>
-    <col min="27" max="27" width="8.85546875" customWidth="1"/>
+    <col min="17" max="17" width="6.88671875" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" customWidth="1"/>
+    <col min="21" max="21" width="14.44140625" customWidth="1"/>
+    <col min="22" max="22" width="8.88671875" style="5"/>
+    <col min="24" max="24" width="8.88671875" style="11"/>
+    <col min="27" max="27" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -832,7 +856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -898,7 +922,7 @@
       <c r="AA2" s="12"/>
       <c r="AB2" s="12"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -982,7 +1006,7 @@
       <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1068,7 +1092,7 @@
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1153,7 +1177,7 @@
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1238,7 +1262,7 @@
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1323,7 +1347,7 @@
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1355,7 +1379,7 @@
         <v>46059.92</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" ref="L8:L12" si="5">2000+3000</f>
+        <f t="shared" ref="L8:L15" si="5">2000+3000</f>
         <v>5000</v>
       </c>
       <c r="M8" s="2">
@@ -1408,7 +1432,7 @@
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1493,7 +1517,7 @@
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1578,7 +1602,7 @@
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1665,7 +1689,7 @@
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1705,7 +1729,7 @@
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="4">
-        <f t="shared" ref="O11:O12" si="28">SUM(L12:M12)</f>
+        <f t="shared" ref="O12" si="28">SUM(L12:M12)</f>
         <v>5000</v>
       </c>
       <c r="P12" s="8">
@@ -1750,7 +1774,7 @@
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1780,121 +1804,123 @@
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="4">
-        <v>43689</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="8">
-        <f>SUM(D14:F14)</f>
-        <v>43689</v>
-      </c>
-      <c r="H14" s="2">
-        <f>10%*G14</f>
-        <v>4368.9000000000005</v>
-      </c>
-      <c r="I14" s="2">
-        <v>400</v>
-      </c>
-      <c r="J14" s="2">
-        <f>6%*G14</f>
-        <v>2621.3399999999997</v>
-      </c>
-      <c r="K14" s="8">
-        <f>SUM(G14:J14)</f>
-        <v>51079.24</v>
-      </c>
-      <c r="L14" s="2">
-        <f>2000+3000</f>
-        <v>5000</v>
-      </c>
-      <c r="M14" s="2">
-        <v>0</v>
-      </c>
+      <c r="G14" s="8"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="4">
-        <f>SUM(L14:M14)</f>
-        <v>5000</v>
-      </c>
-      <c r="P14" s="8">
-        <f>K14+O14</f>
-        <v>56079.24</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>801</v>
-      </c>
-      <c r="R14" s="2">
-        <f>H14*2</f>
-        <v>8737.8000000000011</v>
-      </c>
-      <c r="S14" s="2">
-        <v>1000</v>
-      </c>
+      <c r="O14" s="4"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="2">
-        <f>J14*2</f>
-        <v>5242.6799999999994</v>
-      </c>
-      <c r="V14" s="4">
-        <f>SUM(Q14:U14)</f>
-        <v>15781.48</v>
-      </c>
-      <c r="W14" s="2">
-        <f>X14+U14</f>
-        <v>45540.439999999995</v>
-      </c>
-      <c r="X14" s="10">
-        <f>P14-V14</f>
-        <v>40297.759999999995</v>
-      </c>
-      <c r="Y14" s="2">
-        <f>IF(X14*13&gt;600000,1%*X14,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="2">
-        <f>X14-Y14</f>
-        <v>40297.759999999995</v>
-      </c>
+      <c r="U14" s="2"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="D15" s="4">
+        <f>34730*1.1</f>
+        <v>38203</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" ref="E15" si="29">ROUNDUP(D15/30,0)*4</f>
+        <v>5096</v>
+      </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="G15" s="8">
+        <f t="shared" ref="G15" si="30">SUM(D15:F15)</f>
+        <v>43299</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" ref="H15" si="31">10%*G15</f>
+        <v>4329.9000000000005</v>
+      </c>
+      <c r="I15" s="2">
+        <v>400</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" ref="J15" si="32">6%*G15</f>
+        <v>2597.94</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" ref="K15" si="33">SUM(G15:J15)</f>
+        <v>50626.840000000004</v>
+      </c>
+      <c r="L15" s="2">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
       <c r="N15" s="2"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+      <c r="O15" s="4">
+        <f t="shared" ref="O15" si="34">SUM(L15:M15)</f>
+        <v>5000</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" ref="P15" si="35">K15+O15</f>
+        <v>55626.840000000004</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>800</v>
+      </c>
+      <c r="R15" s="2">
+        <f t="shared" ref="R15" si="36">H15*2</f>
+        <v>8659.8000000000011</v>
+      </c>
+      <c r="S15" s="2">
+        <v>5000</v>
+      </c>
       <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="4"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
+      <c r="U15" s="2">
+        <f t="shared" ref="U15" si="37">J15*2</f>
+        <v>5195.88</v>
+      </c>
+      <c r="V15" s="4">
+        <f t="shared" ref="V15" si="38">SUM(Q15:U15)</f>
+        <v>19655.68</v>
+      </c>
+      <c r="W15" s="2">
+        <f t="shared" ref="W15" si="39">X15+U15</f>
+        <v>41167.040000000001</v>
+      </c>
+      <c r="X15" s="10">
+        <f t="shared" ref="X15" si="40">P15-V15</f>
+        <v>35971.160000000003</v>
+      </c>
+      <c r="Y15" s="2">
+        <f t="shared" ref="Y15" si="41">IF(X15*13&gt;600000,1%*X15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="2">
+        <f t="shared" ref="Z15" si="42">X15-Y15</f>
+        <v>35971.160000000003</v>
+      </c>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1924,37 +1950,91 @@
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="D17" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="G17" s="8">
+        <f>SUM(D17:F17)</f>
+        <v>43689</v>
+      </c>
+      <c r="H17" s="2">
+        <f>10%*G17</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I17" s="2">
+        <v>400</v>
+      </c>
+      <c r="J17" s="2">
+        <f>6%*G17</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K17" s="8">
+        <f>SUM(G17:J17)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L17" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
       <c r="N17" s="2"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
+      <c r="O17" s="4">
+        <f>SUM(L17:M17)</f>
+        <v>5000</v>
+      </c>
+      <c r="P17" s="8">
+        <f>K17+O17</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>801</v>
+      </c>
+      <c r="R17" s="2">
+        <f>H17*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S17" s="2">
+        <v>1000</v>
+      </c>
       <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
+      <c r="U17" s="2">
+        <f>J17*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V17" s="4">
+        <f>SUM(Q17:U17)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="W17" s="2">
+        <f>X17+U17</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="X17" s="10">
+        <f>P17-V17</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Y17" s="2">
+        <f>IF(X17*13&gt;600000,1%*X17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="2">
+        <f>X17-Y17</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -1984,7 +2064,7 @@
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2014,7 +2094,7 @@
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2044,7 +2124,7 @@
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2074,7 +2154,7 @@
       <c r="AA21" s="2"/>
       <c r="AB21" s="2"/>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2104,7 +2184,7 @@
       <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2134,7 +2214,7 @@
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2164,6 +2244,96 @@
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
     </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="W1:W2"/>

--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\082_083\ward1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AE2B73-7096-4B47-8010-4005B5067AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,13 +34,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>User</author>
     <author>DELL</author>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0" shapeId="0">
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -63,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -87,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -111,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -135,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -157,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0" shapeId="0">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -179,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -201,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0">
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -225,7 +226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0">
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -249,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="1" shapeId="0">
+    <comment ref="D15" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -373,7 +374,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -774,31 +775,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="5" width="8.88671875" style="5"/>
-    <col min="6" max="6" width="6.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="9"/>
-    <col min="11" max="11" width="8.88671875" style="9"/>
-    <col min="13" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="5"/>
+    <col min="6" max="6" width="6.28515625" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="9"/>
+    <col min="11" max="11" width="8.85546875" style="9"/>
+    <col min="13" max="13" width="7.28515625" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="5" customWidth="1"/>
     <col min="16" max="16" width="8" style="9" customWidth="1"/>
-    <col min="17" max="17" width="6.88671875" customWidth="1"/>
-    <col min="18" max="18" width="7.6640625" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" customWidth="1"/>
-    <col min="21" max="21" width="14.44140625" customWidth="1"/>
-    <col min="22" max="22" width="8.88671875" style="5"/>
-    <col min="24" max="24" width="8.88671875" style="11"/>
-    <col min="27" max="27" width="8.88671875" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" customWidth="1"/>
+    <col min="18" max="18" width="7.7109375" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="5"/>
+    <col min="24" max="24" width="8.85546875" style="11"/>
+    <col min="27" max="27" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -856,7 +857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -922,7 +923,7 @@
       <c r="AA2" s="12"/>
       <c r="AB2" s="12"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1006,7 +1007,7 @@
       <c r="AA3" s="2"/>
       <c r="AB3" s="2"/>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1092,7 +1093,7 @@
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1177,7 +1178,7 @@
       <c r="AA5" s="2"/>
       <c r="AB5" s="2"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1262,7 +1263,7 @@
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1347,7 +1348,7 @@
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1432,7 +1433,7 @@
       <c r="AA8" s="2"/>
       <c r="AB8" s="2"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1517,7 +1518,7 @@
       <c r="AA9" s="2"/>
       <c r="AB9" s="2"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1602,7 +1603,7 @@
       <c r="AA10" s="2"/>
       <c r="AB10" s="2"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1689,7 +1690,7 @@
       <c r="AA11" s="2"/>
       <c r="AB11" s="2"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1774,7 +1775,7 @@
       <c r="AA12" s="2"/>
       <c r="AB12" s="2"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1804,7 +1805,7 @@
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1834,7 +1835,7 @@
       <c r="AA14" s="2"/>
       <c r="AB14" s="2"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1871,16 +1872,17 @@
         <v>5000</v>
       </c>
       <c r="M15" s="2">
-        <v>0</v>
+        <f>10%*D15</f>
+        <v>3820.3</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="4">
         <f t="shared" ref="O15" si="34">SUM(L15:M15)</f>
-        <v>5000</v>
+        <v>8820.2999999999993</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15" si="35">K15+O15</f>
-        <v>55626.840000000004</v>
+        <v>59447.14</v>
       </c>
       <c r="Q15" s="2">
         <v>800</v>
@@ -1903,11 +1905,11 @@
       </c>
       <c r="W15" s="2">
         <f t="shared" ref="W15" si="39">X15+U15</f>
-        <v>41167.040000000001</v>
+        <v>44987.34</v>
       </c>
       <c r="X15" s="10">
         <f t="shared" ref="X15" si="40">P15-V15</f>
-        <v>35971.160000000003</v>
+        <v>39791.46</v>
       </c>
       <c r="Y15" s="2">
         <f t="shared" ref="Y15" si="41">IF(X15*13&gt;600000,1%*X15,0)</f>
@@ -1915,12 +1917,12 @@
       </c>
       <c r="Z15" s="2">
         <f t="shared" ref="Z15" si="42">X15-Y15</f>
-        <v>35971.160000000003</v>
+        <v>39791.46</v>
       </c>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1950,7 +1952,7 @@
       <c r="AA16" s="2"/>
       <c r="AB16" s="2"/>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2034,7 +2036,7 @@
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2064,7 +2066,7 @@
       <c r="AA18" s="2"/>
       <c r="AB18" s="2"/>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2094,7 +2096,7 @@
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2124,7 +2126,7 @@
       <c r="AA20" s="2"/>
       <c r="AB20" s="2"/>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2154,7 +2156,7 @@
       <c r="AA21" s="2"/>
       <c r="AB21" s="2"/>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2184,7 +2186,7 @@
       <c r="AA22" s="2"/>
       <c r="AB22" s="2"/>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2214,7 +2216,7 @@
       <c r="AA23" s="2"/>
       <c r="AB23" s="2"/>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2244,7 +2246,7 @@
       <c r="AA24" s="2"/>
       <c r="AB24" s="2"/>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2274,7 +2276,7 @@
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2304,7 +2306,7 @@
       <c r="AA26" s="2"/>
       <c r="AB26" s="2"/>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>

--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AE2B73-7096-4B47-8010-4005B5067AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A194D81C-9892-4ACE-92FC-2F17353849E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -250,7 +250,103 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{5D35B49C-F6A5-44F5-BD0B-3CCA5B32ED71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+jestha</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{CC553876-1D1F-402D-BAD2-E6D2FCB02EB8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Asadh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{5B7F8F01-034B-4B9A-A2C9-B8CCCEC88184}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Asadh grade bridhhi</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0" shapeId="0" xr:uid="{BBB80961-844E-4A46-AB15-ECDE6FEA2261}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+asadh anugaman bhatta 2083/03/25</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D17" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -279,7 +375,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>l;= g+=</t>
   </si>
@@ -369,12 +465,18 @@
   </si>
   <si>
     <t>cGo eQf -rfF8kj{ vr{_</t>
+  </si>
+  <si>
+    <t>Asadh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -468,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -496,6 +598,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,27 +879,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="5" width="8.85546875" style="5"/>
-    <col min="6" max="6" width="6.28515625" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="9"/>
-    <col min="11" max="11" width="8.85546875" style="9"/>
-    <col min="13" max="13" width="7.28515625" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" style="5" customWidth="1"/>
-    <col min="16" max="16" width="8" style="9" customWidth="1"/>
-    <col min="17" max="17" width="6.85546875" customWidth="1"/>
-    <col min="18" max="18" width="7.7109375" customWidth="1"/>
-    <col min="20" max="20" width="8.85546875" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" customWidth="1"/>
-    <col min="22" max="22" width="8.85546875" style="5"/>
-    <col min="24" max="24" width="8.85546875" style="11"/>
-    <col min="27" max="27" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.85546875" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1082,11 +1193,11 @@
         <f>P4-V4</f>
         <v>72026.080000000002</v>
       </c>
-      <c r="Y4" s="2">
+      <c r="Y4" s="15">
         <f>IF(X4*13&gt;600000,1%*X4,0)</f>
         <v>720.26080000000002</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Z4" s="15">
         <f>X4-Y4</f>
         <v>71305.819199999998</v>
       </c>
@@ -1380,7 +1491,7 @@
         <v>46059.92</v>
       </c>
       <c r="L8" s="2">
-        <f t="shared" ref="L8:L15" si="5">2000+3000</f>
+        <f t="shared" ref="L8:L17" si="5">2000+3000</f>
         <v>5000</v>
       </c>
       <c r="M8" s="2">
@@ -1779,29 +1890,84 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
+      <c r="D13" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" ref="E13" si="29">ROUNDUP(D13/30,0)*4</f>
+        <v>4632</v>
+      </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="G13" s="8">
+        <f t="shared" ref="G13" si="30">SUM(D13:F13)</f>
+        <v>39362</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" ref="H13" si="31">10%*G13</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I13" s="2">
+        <v>400</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" ref="J13" si="32">6%*G13</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" ref="K13" si="33">SUM(G13:J13)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L13" s="2">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
       <c r="N13" s="2"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
+      <c r="O13" s="4">
+        <f t="shared" ref="O13" si="34">SUM(L13:M13)</f>
+        <v>5000</v>
+      </c>
+      <c r="P13" s="8">
+        <f t="shared" ref="P13" si="35">K13+O13</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>800</v>
+      </c>
+      <c r="R13" s="2">
+        <f t="shared" ref="R13" si="36">H13*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S13" s="2">
+        <v>5000</v>
+      </c>
       <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
+      <c r="U13" s="2">
+        <f t="shared" ref="U13" si="37">J13*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V13" s="4">
+        <f t="shared" ref="V13" si="38">SUM(Q13:U13)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W13" s="2">
+        <f t="shared" ref="W13" si="39">X13+U13</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X13" s="10">
+        <f t="shared" ref="X13" si="40">P13-V13</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y13" s="2">
+        <f t="shared" ref="Y13" si="41">IF(X13*13&gt;600000,1%*X13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2">
+        <f t="shared" ref="Z13" si="42">X13-Y13</f>
+        <v>32664.079999999998</v>
+      </c>
       <c r="AA13" s="2"/>
       <c r="AB13" s="2"/>
     </row>
@@ -1809,116 +1975,120 @@
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
+      <c r="D14" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E14" s="4">
+        <f>ROUNDUP(D14/30,0)*5</f>
+        <v>5790</v>
+      </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="G14" s="8">
+        <f t="shared" ref="G14" si="43">SUM(D14:F14)</f>
+        <v>40520</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" ref="H14" si="44">10%*G14</f>
+        <v>4052</v>
+      </c>
+      <c r="I14" s="2">
+        <v>400</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" ref="J14" si="45">6%*G14</f>
+        <v>2431.1999999999998</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" ref="K14" si="46">SUM(G14:J14)</f>
+        <v>47403.199999999997</v>
+      </c>
+      <c r="L14" s="2">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
       <c r="N14" s="2"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="O14" s="4">
+        <f t="shared" ref="O14" si="47">SUM(L14:M14)</f>
+        <v>5000</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" ref="P14" si="48">K14+O14</f>
+        <v>52403.199999999997</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>800</v>
+      </c>
+      <c r="R14" s="2">
+        <f t="shared" ref="R14" si="49">H14*2</f>
+        <v>8104</v>
+      </c>
+      <c r="S14" s="2">
+        <v>5000</v>
+      </c>
       <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="4"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
+      <c r="U14" s="2">
+        <f t="shared" ref="U14" si="50">J14*2</f>
+        <v>4862.3999999999996</v>
+      </c>
+      <c r="V14" s="4">
+        <f t="shared" ref="V14" si="51">SUM(Q14:U14)</f>
+        <v>18766.400000000001</v>
+      </c>
+      <c r="W14" s="2">
+        <f t="shared" ref="W14" si="52">X14+U14</f>
+        <v>38499.199999999997</v>
+      </c>
+      <c r="X14" s="10">
+        <f t="shared" ref="X14" si="53">P14-V14</f>
+        <v>33636.799999999996</v>
+      </c>
+      <c r="Y14" s="2">
+        <f t="shared" ref="Y14" si="54">IF(X14*13&gt;600000,1%*X14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2">
+        <f t="shared" ref="Z14" si="55">X14-Y14</f>
+        <v>33636.799999999996</v>
+      </c>
       <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
+      <c r="AB14" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="4">
-        <f>34730*1.1</f>
-        <v>38203</v>
-      </c>
-      <c r="E15" s="4">
-        <f t="shared" ref="E15" si="29">ROUNDUP(D15/30,0)*4</f>
-        <v>5096</v>
-      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="8">
-        <f t="shared" ref="G15" si="30">SUM(D15:F15)</f>
-        <v>43299</v>
-      </c>
-      <c r="H15" s="2">
-        <f t="shared" ref="H15" si="31">10%*G15</f>
-        <v>4329.9000000000005</v>
-      </c>
-      <c r="I15" s="2">
-        <v>400</v>
-      </c>
-      <c r="J15" s="2">
-        <f t="shared" ref="J15" si="32">6%*G15</f>
-        <v>2597.94</v>
-      </c>
+      <c r="G15" s="8"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
       <c r="K15" s="8">
-        <f t="shared" ref="K15" si="33">SUM(G15:J15)</f>
-        <v>50626.840000000004</v>
-      </c>
-      <c r="L15" s="2">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L15" s="2"/>
       <c r="M15" s="2">
-        <f>10%*D15</f>
-        <v>3820.3</v>
+        <v>5100</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" s="4">
-        <f t="shared" ref="O15" si="34">SUM(L15:M15)</f>
-        <v>8820.2999999999993</v>
-      </c>
-      <c r="P15" s="8">
-        <f t="shared" ref="P15" si="35">K15+O15</f>
-        <v>59447.14</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>800</v>
-      </c>
-      <c r="R15" s="2">
-        <f t="shared" ref="R15" si="36">H15*2</f>
-        <v>8659.8000000000011</v>
-      </c>
-      <c r="S15" s="2">
-        <v>5000</v>
-      </c>
+      <c r="O15" s="4"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
       <c r="T15" s="2"/>
-      <c r="U15" s="2">
-        <f t="shared" ref="U15" si="37">J15*2</f>
-        <v>5195.88</v>
-      </c>
-      <c r="V15" s="4">
-        <f t="shared" ref="V15" si="38">SUM(Q15:U15)</f>
-        <v>19655.68</v>
-      </c>
-      <c r="W15" s="2">
-        <f t="shared" ref="W15" si="39">X15+U15</f>
-        <v>44987.34</v>
-      </c>
-      <c r="X15" s="10">
-        <f t="shared" ref="X15" si="40">P15-V15</f>
-        <v>39791.46</v>
-      </c>
-      <c r="Y15" s="2">
-        <f t="shared" ref="Y15" si="41">IF(X15*13&gt;600000,1%*X15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="2">
-        <f t="shared" ref="Z15" si="42">X15-Y15</f>
-        <v>39791.46</v>
-      </c>
+      <c r="U15" s="2"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
       <c r="AB15" s="2"/>
     </row>
@@ -1957,81 +2127,84 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="4">
-        <v>43689</v>
+        <f>34730*1.1</f>
+        <v>38203</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <f>ROUNDUP(D17/30,0)*4</f>
+        <v>5096</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="8">
-        <f>SUM(D17:F17)</f>
-        <v>43689</v>
+        <f t="shared" ref="G17" si="56">SUM(D17:F17)</f>
+        <v>43299</v>
       </c>
       <c r="H17" s="2">
-        <f>10%*G17</f>
-        <v>4368.9000000000005</v>
+        <f t="shared" ref="H17" si="57">10%*G17</f>
+        <v>4329.9000000000005</v>
       </c>
       <c r="I17" s="2">
         <v>400</v>
       </c>
       <c r="J17" s="2">
-        <f>6%*G17</f>
-        <v>2621.3399999999997</v>
+        <f t="shared" ref="J17" si="58">6%*G17</f>
+        <v>2597.94</v>
       </c>
       <c r="K17" s="8">
-        <f>SUM(G17:J17)</f>
-        <v>51079.24</v>
+        <f t="shared" ref="K17" si="59">SUM(G17:J17)</f>
+        <v>50626.840000000004</v>
       </c>
       <c r="L17" s="2">
-        <f>2000+3000</f>
+        <f t="shared" si="5"/>
         <v>5000</v>
       </c>
       <c r="M17" s="2">
-        <v>0</v>
+        <f>10%*D17</f>
+        <v>3820.3</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="4">
-        <f>SUM(L17:M17)</f>
-        <v>5000</v>
+        <f t="shared" ref="O17" si="60">SUM(L17:M17)</f>
+        <v>8820.2999999999993</v>
       </c>
       <c r="P17" s="8">
-        <f>K17+O17</f>
-        <v>56079.24</v>
+        <f t="shared" ref="P17" si="61">K17+O17</f>
+        <v>59447.14</v>
       </c>
       <c r="Q17" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="R17" s="2">
-        <f>H17*2</f>
-        <v>8737.8000000000011</v>
+        <f t="shared" ref="R17" si="62">H17*2</f>
+        <v>8659.8000000000011</v>
       </c>
       <c r="S17" s="2">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T17" s="2"/>
       <c r="U17" s="2">
-        <f>J17*2</f>
-        <v>5242.6799999999994</v>
+        <f t="shared" ref="U17" si="63">J17*2</f>
+        <v>5195.88</v>
       </c>
       <c r="V17" s="4">
-        <f>SUM(Q17:U17)</f>
-        <v>15781.48</v>
+        <f t="shared" ref="V17" si="64">SUM(Q17:U17)</f>
+        <v>19655.68</v>
       </c>
       <c r="W17" s="2">
-        <f>X17+U17</f>
-        <v>45540.439999999995</v>
+        <f t="shared" ref="W17" si="65">X17+U17</f>
+        <v>44987.34</v>
       </c>
       <c r="X17" s="10">
-        <f>P17-V17</f>
-        <v>40297.759999999995</v>
+        <f t="shared" ref="X17" si="66">P17-V17</f>
+        <v>39791.46</v>
       </c>
       <c r="Y17" s="2">
-        <f>IF(X17*13&gt;600000,1%*X17,0)</f>
+        <f t="shared" ref="Y17" si="67">IF(X17*13&gt;600000,1%*X17,0)</f>
         <v>0</v>
       </c>
       <c r="Z17" s="2">
-        <f>X17-Y17</f>
-        <v>40297.759999999995</v>
+        <f t="shared" ref="Z17" si="68">X17-Y17</f>
+        <v>39791.46</v>
       </c>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
@@ -2070,29 +2243,83 @@
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="D19" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+      <c r="G19" s="8">
+        <f>SUM(D19:F19)</f>
+        <v>43689</v>
+      </c>
+      <c r="H19" s="2">
+        <f>10%*G19</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I19" s="2">
+        <v>400</v>
+      </c>
+      <c r="J19" s="2">
+        <f>6%*G19</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K19" s="8">
+        <f>SUM(G19:J19)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L19" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
       <c r="N19" s="2"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
+      <c r="O19" s="4">
+        <f>SUM(L19:M19)</f>
+        <v>5000</v>
+      </c>
+      <c r="P19" s="8">
+        <f>K19+O19</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>801</v>
+      </c>
+      <c r="R19" s="2">
+        <f>H19*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S19" s="2">
+        <v>1000</v>
+      </c>
       <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
+      <c r="U19" s="2">
+        <f>J19*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V19" s="4">
+        <f>SUM(Q19:U19)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="W19" s="2">
+        <f>X19+U19</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="X19" s="10">
+        <f>P19-V19</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Y19" s="2">
+        <f>IF(X19*13&gt;600000,1%*X19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
+        <f>X19-Y19</f>
+        <v>40297.759999999995</v>
+      </c>
       <c r="AA19" s="2"/>
       <c r="AB19" s="2"/>
     </row>
@@ -2336,6 +2563,66 @@
       <c r="AA27" s="2"/>
       <c r="AB27" s="2"/>
     </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="W1:W2"/>

--- a/New Microsoft Excel Worksheet.xlsx
+++ b/New Microsoft Excel Worksheet.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A194D81C-9892-4ACE-92FC-2F17353849E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696165D7-3355-426F-BC0E-AECE6F603F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="for check" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -374,8 +375,757 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+    <author>DELL</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{B868339A-E22D-43B4-B7DD-A5CCA0F0A9F2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Asadh 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{838E0AB7-3511-4264-8B53-DB7A8A6000AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Shrawan 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{CE997E4B-CC82-4638-9E10-66EE82621F70}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Aswin 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{D5F3039C-9AA2-4478-8177-A80D5CC4D355}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Chaitra 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{0101992F-2016-4611-A038-5D398A7E8674}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Shrawan 2078</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{406F2FD4-59C2-49D7-B564-FACFDEAEC2D3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Aswin 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{57F0913E-FB11-443D-8D0E-50C3A3BE63FB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Chaitra 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{61922606-D422-4B14-B4D2-F2F64C89FC03}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Shrawan 2079</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{1CD94DED-B9CE-48AB-A1D4-907EBF923352}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Aswin 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D39" authorId="0" shapeId="0" xr:uid="{F67E3D40-751F-45CD-9A8D-F5FF36BA84C7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Chaitra 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D44" authorId="0" shapeId="0" xr:uid="{F1737FF4-EAC3-46E7-B74D-92CAFDE4E96F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Shrawan 2080</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D46" authorId="0" shapeId="0" xr:uid="{35E0968B-D5F9-4101-B904-661AA4637E19}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Aswin 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D52" authorId="0" shapeId="0" xr:uid="{0A295F54-8C85-4B00-A407-63F1240626E2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Chaitra 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D57" authorId="0" shapeId="0" xr:uid="{363930B6-DF27-4439-8BB5-BA6DBB3A62F5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Shrawan 2080</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D59" authorId="0" shapeId="0" xr:uid="{125070B4-9D32-4BFD-99C1-58A911007603}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Aswin 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D65" authorId="0" shapeId="0" xr:uid="{76612F6F-4157-4FB6-B7FF-3FB8BDE4E850}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Chaitra 2077</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D70" authorId="0" shapeId="0" xr:uid="{8EC8D1FA-2BB9-448C-AE95-0915B309B4CE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Shrawan 2082/2083</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D71" authorId="0" shapeId="0" xr:uid="{7D3038DB-5E71-4E9B-AA13-B0DC69356A9F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+bhadra</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D72" authorId="0" shapeId="0" xr:uid="{8FA0EC66-86EE-4469-AF70-BF83FB22E028}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Ashwin</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D73" authorId="0" shapeId="0" xr:uid="{2D8F676D-98DE-448C-B00F-BF44175C6821}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Kartik</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D74" authorId="0" shapeId="0" xr:uid="{2DD03DC4-0819-4F4B-BB0C-94EC7468EE86}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Mangsir</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D75" authorId="0" shapeId="0" xr:uid="{48E7EB78-3897-4809-A954-24EC7EB99C5A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+poush</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D76" authorId="0" shapeId="0" xr:uid="{5600AD6D-48E0-4FBF-87BE-A609E5658122}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+Magh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D77" authorId="0" shapeId="0" xr:uid="{3FF119A5-131C-47C5-B06E-FF897516B77B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+falgun</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D78" authorId="0" shapeId="0" xr:uid="{0F9FCA2B-CE09-43CC-B4FD-9F40F5A91853}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+chaitra</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D79" authorId="0" shapeId="0" xr:uid="{86C840E2-6462-4446-AF90-A8B3FF00F4BF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Baisakh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D80" authorId="0" shapeId="0" xr:uid="{5D51E2EE-A448-4389-A372-E4BBFB552B7F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+jestha</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D81" authorId="0" shapeId="0" xr:uid="{AB12CF4D-CD25-494A-BB9C-AF11A084B26F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Asadh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E81" authorId="0" shapeId="0" xr:uid="{3834E43B-C7B9-403D-9AB6-404396A32B80}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Asadh grade bridhhi</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M82" authorId="0" shapeId="0" xr:uid="{DF0DAF17-9556-4E92-8611-A136E25F8C2E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+asadh anugaman bhatta 2083/03/25</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D84" authorId="1" shapeId="0" xr:uid="{77C76E6E-8187-405C-85F2-C4B071248F14}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>DELL:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+From shrawan</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="31">
   <si>
     <t>l;= g+=</t>
   </si>
@@ -475,7 +1225,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -589,6 +1339,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -598,7 +1349,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -911,67 +1661,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13" t="s">
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13" t="s">
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="14" t="s">
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="12" t="s">
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="X1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="Y1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="12" t="s">
+      <c r="Z1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="12" t="s">
+      <c r="AA1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="12" t="s">
+      <c r="AB1" s="13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1008,7 +1758,7 @@
       <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="14"/>
+      <c r="P2" s="15"/>
       <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
@@ -1027,12 +1777,12 @@
       <c r="V2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -1193,11 +1943,11 @@
         <f>P4-V4</f>
         <v>72026.080000000002</v>
       </c>
-      <c r="Y4" s="15">
+      <c r="Y4" s="12">
         <f>IF(X4*13&gt;600000,1%*X4,0)</f>
         <v>720.26080000000002</v>
       </c>
-      <c r="Z4" s="15">
+      <c r="Z4" s="12">
         <f>X4-Y4</f>
         <v>71305.819199999998</v>
       </c>
@@ -2644,4 +3394,7199 @@
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC65475-327E-4983-B60B-CF7593014FA5}">
+  <dimension ref="A1:AB96"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.85546875" customWidth="1"/>
+    <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" s="6" customFormat="1" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W2" s="13"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+    </row>
+    <row r="3" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="8">
+        <f t="shared" ref="G3" si="0">SUM(D3:F3)</f>
+        <v>26610</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H66" si="1">10%*G3</f>
+        <v>2661</v>
+      </c>
+      <c r="I3" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3" si="2">6%*G3</f>
+        <v>1596.6</v>
+      </c>
+      <c r="K3" s="8">
+        <f t="shared" ref="K3" si="3">SUM(G3:J3)</f>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <f>10%*D3</f>
+        <v>2661</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="4">
+        <f>SUM(L3:N3)</f>
+        <v>2661</v>
+      </c>
+      <c r="P3" s="8">
+        <f t="shared" ref="P3" si="4">K3+O3</f>
+        <v>33928.6</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>800</v>
+      </c>
+      <c r="R3" s="2">
+        <f t="shared" ref="R3" si="5">H3*2</f>
+        <v>5322</v>
+      </c>
+      <c r="S3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2">
+        <f t="shared" ref="U3" si="6">J3*2</f>
+        <v>3193.2</v>
+      </c>
+      <c r="V3" s="4">
+        <f t="shared" ref="V3" si="7">SUM(Q3:U3)</f>
+        <v>14315.2</v>
+      </c>
+      <c r="W3" s="2">
+        <f t="shared" ref="W3" si="8">X3+U3</f>
+        <v>22806.6</v>
+      </c>
+      <c r="X3" s="10">
+        <f t="shared" ref="X3" si="9">P3-V3</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y3" s="2">
+        <f t="shared" ref="Y3:Y66" si="10">IF(X3*13&gt;600000,1%*X3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2">
+        <f t="shared" ref="Z3" si="11">X3-Y3</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+    </row>
+    <row r="4" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+    </row>
+    <row r="5" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E5" s="4">
+        <f>ROUNDUP(D5/30,0)*0</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="8">
+        <f t="shared" ref="G5:G16" si="12">SUM(D5:F5)</f>
+        <v>26610</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I5" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" ref="J5:J16" si="13">6%*G5</f>
+        <v>1596.6</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" ref="K5:K16" si="14">SUM(G5:J5)</f>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <f>10%*D5</f>
+        <v>2661</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="4">
+        <f t="shared" ref="O5:O16" si="15">SUM(L5:N5)</f>
+        <v>2661</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" ref="P5:P16" si="16">K5+O5</f>
+        <v>33928.6</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>800</v>
+      </c>
+      <c r="R5" s="2">
+        <f t="shared" ref="R5:R16" si="17">H5*2</f>
+        <v>5322</v>
+      </c>
+      <c r="S5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2">
+        <f t="shared" ref="U5:U16" si="18">J5*2</f>
+        <v>3193.2</v>
+      </c>
+      <c r="V5" s="4">
+        <f t="shared" ref="V5:V16" si="19">SUM(Q5:U5)</f>
+        <v>14315.2</v>
+      </c>
+      <c r="W5" s="2">
+        <f t="shared" ref="W5:W16" si="20">X5+U5</f>
+        <v>22806.6</v>
+      </c>
+      <c r="X5" s="10">
+        <f t="shared" ref="X5:X16" si="21">P5-V5</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y5" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="2">
+        <f t="shared" ref="Z5:Z16" si="22">X5-Y5</f>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+    </row>
+    <row r="6" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" ref="E6:E15" si="23">ROUNDUP(D6/30,0)*0</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I6" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K6" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <f>10%*D6</f>
+        <v>2661</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P6" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>800</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S6" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W6" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X6" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y6" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+    </row>
+    <row r="7" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I7" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <f>10%*D7+D7</f>
+        <v>29271</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="4">
+        <f t="shared" si="15"/>
+        <v>29271</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="16"/>
+        <v>60538.6</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>800</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S7" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V7" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W7" s="2">
+        <f t="shared" si="20"/>
+        <v>49416.599999999991</v>
+      </c>
+      <c r="X7" s="10">
+        <f t="shared" si="21"/>
+        <v>46223.399999999994</v>
+      </c>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2">
+        <f t="shared" si="22"/>
+        <v>46223.399999999994</v>
+      </c>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+    </row>
+    <row r="8" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I8" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K8" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <f>10%*D8</f>
+        <v>2661</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P8" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>800</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S8" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V8" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W8" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X8" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y8" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+    </row>
+    <row r="9" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I9" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K9" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <f>10%*D9</f>
+        <v>2661</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P9" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>800</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S9" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V9" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W9" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X9" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y9" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+    </row>
+    <row r="10" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I10" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K10" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <f>10%*D10</f>
+        <v>2661</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P10" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>800</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S10" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V10" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W10" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X10" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y10" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+    </row>
+    <row r="11" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E11" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I11" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <f>10%*D11</f>
+        <v>2661</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P11" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>800</v>
+      </c>
+      <c r="R11" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S11" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V11" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W11" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X11" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y11" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+    </row>
+    <row r="12" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I12" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K12" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <f>10%*D12</f>
+        <v>2661</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P12" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>800</v>
+      </c>
+      <c r="R12" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S12" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V12" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W12" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X12" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y12" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+    </row>
+    <row r="13" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I13" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K13" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <f>10%*D13</f>
+        <v>2661</v>
+      </c>
+      <c r="N13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O13" s="4">
+        <f t="shared" si="15"/>
+        <v>12661</v>
+      </c>
+      <c r="P13" s="8">
+        <f t="shared" si="16"/>
+        <v>43928.6</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>800</v>
+      </c>
+      <c r="R13" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S13" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V13" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W13" s="2">
+        <f t="shared" si="20"/>
+        <v>32806.6</v>
+      </c>
+      <c r="X13" s="10">
+        <f t="shared" si="21"/>
+        <v>29613.399999999998</v>
+      </c>
+      <c r="Y13" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2">
+        <f t="shared" si="22"/>
+        <v>29613.399999999998</v>
+      </c>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+    </row>
+    <row r="14" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I14" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <f>10%*D14</f>
+        <v>2661</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>800</v>
+      </c>
+      <c r="R14" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S14" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V14" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W14" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X14" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y14" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+    </row>
+    <row r="15" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="8">
+        <f t="shared" si="12"/>
+        <v>26610</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>2661</v>
+      </c>
+      <c r="I15" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="13"/>
+        <v>1596.6</v>
+      </c>
+      <c r="K15" s="8">
+        <f t="shared" si="14"/>
+        <v>31267.599999999999</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <f>10%*D15</f>
+        <v>2661</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" si="16"/>
+        <v>33928.6</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>800</v>
+      </c>
+      <c r="R15" s="2">
+        <f t="shared" si="17"/>
+        <v>5322</v>
+      </c>
+      <c r="S15" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2">
+        <f t="shared" si="18"/>
+        <v>3193.2</v>
+      </c>
+      <c r="V15" s="4">
+        <f t="shared" si="19"/>
+        <v>14315.2</v>
+      </c>
+      <c r="W15" s="2">
+        <f t="shared" si="20"/>
+        <v>22806.6</v>
+      </c>
+      <c r="X15" s="10">
+        <f t="shared" si="21"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="Y15" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="2">
+        <f t="shared" si="22"/>
+        <v>19613.399999999998</v>
+      </c>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+    </row>
+    <row r="16" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4">
+        <v>26610</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" ref="E6:E18" si="24">ROUNDUP(D16/30,0)</f>
+        <v>887</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="8">
+        <f t="shared" si="12"/>
+        <v>27497</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>2749.7000000000003</v>
+      </c>
+      <c r="I16" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="13"/>
+        <v>1649.82</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="14"/>
+        <v>32296.52</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <f>10%*D16</f>
+        <v>2661</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="4">
+        <f t="shared" si="15"/>
+        <v>2661</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="16"/>
+        <v>34957.520000000004</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>800</v>
+      </c>
+      <c r="R16" s="2">
+        <f t="shared" si="17"/>
+        <v>5499.4000000000005</v>
+      </c>
+      <c r="S16" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2">
+        <f t="shared" si="18"/>
+        <v>3299.64</v>
+      </c>
+      <c r="V16" s="4">
+        <f t="shared" si="19"/>
+        <v>14599.04</v>
+      </c>
+      <c r="W16" s="2">
+        <f t="shared" si="20"/>
+        <v>23658.120000000003</v>
+      </c>
+      <c r="X16" s="10">
+        <f t="shared" si="21"/>
+        <v>20358.480000000003</v>
+      </c>
+      <c r="Y16" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2">
+        <f t="shared" si="22"/>
+        <v>20358.480000000003</v>
+      </c>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+    </row>
+    <row r="17" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+    </row>
+    <row r="18" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E18" s="4">
+        <f>ROUNDUP(D18/30,0)*1</f>
+        <v>954</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="8">
+        <f t="shared" ref="G18:G29" si="25">SUM(D18:F18)</f>
+        <v>29564</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I18" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" ref="J18:J29" si="26">6%*G18</f>
+        <v>1773.84</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" ref="K18:K29" si="27">SUM(G18:J18)</f>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <f>10%*D18</f>
+        <v>2861</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="4">
+        <f t="shared" ref="O18:O29" si="28">SUM(L18:N18)</f>
+        <v>2861</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" ref="P18:P29" si="29">K18+O18</f>
+        <v>37555.24</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>800</v>
+      </c>
+      <c r="R18" s="2">
+        <f t="shared" ref="R18:R29" si="30">H18*2</f>
+        <v>5912.8</v>
+      </c>
+      <c r="S18" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2">
+        <f t="shared" ref="U18:U29" si="31">J18*2</f>
+        <v>3547.68</v>
+      </c>
+      <c r="V18" s="4">
+        <f t="shared" ref="V18:V29" si="32">SUM(Q18:U18)</f>
+        <v>15260.48</v>
+      </c>
+      <c r="W18" s="2">
+        <f t="shared" ref="W18:W29" si="33">X18+U18</f>
+        <v>25842.44</v>
+      </c>
+      <c r="X18" s="10">
+        <f t="shared" ref="X18:X29" si="34">P18-V18</f>
+        <v>22294.76</v>
+      </c>
+      <c r="Y18" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2">
+        <f t="shared" ref="Z18:Z29" si="35">X18-Y18</f>
+        <v>22294.76</v>
+      </c>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+    </row>
+    <row r="19" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" ref="E19:E28" si="36">ROUNDUP(D19/30,0)*1</f>
+        <v>954</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I19" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K19" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <f>10%*D19</f>
+        <v>2861</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P19" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>800</v>
+      </c>
+      <c r="R19" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S19" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V19" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W19" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X19" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y19" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+    </row>
+    <row r="20" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I20" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <f>10%*D20+D20</f>
+        <v>31471</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="4">
+        <f t="shared" si="28"/>
+        <v>31471</v>
+      </c>
+      <c r="P20" s="8">
+        <f t="shared" si="29"/>
+        <v>66165.239999999991</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>800</v>
+      </c>
+      <c r="R20" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S20" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V20" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W20" s="2">
+        <f t="shared" si="33"/>
+        <v>54452.439999999995</v>
+      </c>
+      <c r="X20" s="10">
+        <f t="shared" si="34"/>
+        <v>50904.759999999995</v>
+      </c>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2">
+        <f t="shared" si="35"/>
+        <v>50904.759999999995</v>
+      </c>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+    </row>
+    <row r="21" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E21" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I21" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
+        <f>10%*D21</f>
+        <v>2861</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P21" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>800</v>
+      </c>
+      <c r="R21" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S21" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V21" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W21" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X21" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y21" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+    </row>
+    <row r="22" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I22" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K22" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <f>10%*D22</f>
+        <v>2861</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P22" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>800</v>
+      </c>
+      <c r="R22" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S22" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V22" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W22" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X22" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y22" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+    </row>
+    <row r="23" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E23" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I23" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J23" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K23" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <f>10%*D23</f>
+        <v>2861</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P23" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>800</v>
+      </c>
+      <c r="R23" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S23" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V23" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W23" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X23" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y23" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+    </row>
+    <row r="24" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I24" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J24" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K24" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <f>10%*D24</f>
+        <v>2861</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P24" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>800</v>
+      </c>
+      <c r="R24" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S24" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V24" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W24" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X24" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y24" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+    </row>
+    <row r="25" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E25" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H25" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I25" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J25" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K25" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <f>10%*D25</f>
+        <v>2861</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P25" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>800</v>
+      </c>
+      <c r="R25" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S25" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V25" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W25" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X25" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y25" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+    </row>
+    <row r="26" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H26" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I26" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J26" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K26" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <f>10%*D26</f>
+        <v>2861</v>
+      </c>
+      <c r="N26" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O26" s="4">
+        <f t="shared" si="28"/>
+        <v>12861</v>
+      </c>
+      <c r="P26" s="8">
+        <f t="shared" si="29"/>
+        <v>47555.24</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>800</v>
+      </c>
+      <c r="R26" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S26" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V26" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W26" s="2">
+        <f t="shared" si="33"/>
+        <v>35842.439999999995</v>
+      </c>
+      <c r="X26" s="10">
+        <f t="shared" si="34"/>
+        <v>32294.76</v>
+      </c>
+      <c r="Y26" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2">
+        <f t="shared" si="35"/>
+        <v>32294.76</v>
+      </c>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+    </row>
+    <row r="27" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E27" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I27" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K27" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <f>10%*D27</f>
+        <v>2861</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P27" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>800</v>
+      </c>
+      <c r="R27" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S27" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V27" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W27" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X27" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y27" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+    </row>
+    <row r="28" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="36"/>
+        <v>954</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="8">
+        <f t="shared" si="25"/>
+        <v>29564</v>
+      </c>
+      <c r="H28" s="2">
+        <f t="shared" si="1"/>
+        <v>2956.4</v>
+      </c>
+      <c r="I28" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" si="26"/>
+        <v>1773.84</v>
+      </c>
+      <c r="K28" s="8">
+        <f t="shared" si="27"/>
+        <v>34694.239999999998</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <f>10%*D28</f>
+        <v>2861</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P28" s="8">
+        <f t="shared" si="29"/>
+        <v>37555.24</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>800</v>
+      </c>
+      <c r="R28" s="2">
+        <f t="shared" si="30"/>
+        <v>5912.8</v>
+      </c>
+      <c r="S28" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2">
+        <f t="shared" si="31"/>
+        <v>3547.68</v>
+      </c>
+      <c r="V28" s="4">
+        <f t="shared" si="32"/>
+        <v>15260.48</v>
+      </c>
+      <c r="W28" s="2">
+        <f t="shared" si="33"/>
+        <v>25842.44</v>
+      </c>
+      <c r="X28" s="10">
+        <f t="shared" si="34"/>
+        <v>22294.76</v>
+      </c>
+      <c r="Y28" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="2">
+        <f t="shared" si="35"/>
+        <v>22294.76</v>
+      </c>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+    </row>
+    <row r="29" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4">
+        <v>28610</v>
+      </c>
+      <c r="E29" s="4">
+        <f>ROUNDUP(D29/30,0)*2</f>
+        <v>1908</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="8">
+        <f t="shared" si="25"/>
+        <v>30518</v>
+      </c>
+      <c r="H29" s="2">
+        <f t="shared" si="1"/>
+        <v>3051.8</v>
+      </c>
+      <c r="I29" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J29" s="2">
+        <f t="shared" si="26"/>
+        <v>1831.08</v>
+      </c>
+      <c r="K29" s="8">
+        <f t="shared" si="27"/>
+        <v>35800.880000000005</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <f>10%*D29</f>
+        <v>2861</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="4">
+        <f t="shared" si="28"/>
+        <v>2861</v>
+      </c>
+      <c r="P29" s="8">
+        <f t="shared" si="29"/>
+        <v>38661.880000000005</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>800</v>
+      </c>
+      <c r="R29" s="2">
+        <f t="shared" si="30"/>
+        <v>6103.6</v>
+      </c>
+      <c r="S29" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2">
+        <f t="shared" si="31"/>
+        <v>3662.16</v>
+      </c>
+      <c r="V29" s="4">
+        <f t="shared" si="32"/>
+        <v>15565.76</v>
+      </c>
+      <c r="W29" s="2">
+        <f t="shared" si="33"/>
+        <v>26758.280000000002</v>
+      </c>
+      <c r="X29" s="10">
+        <f t="shared" si="34"/>
+        <v>23096.120000000003</v>
+      </c>
+      <c r="Y29" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="2">
+        <f t="shared" si="35"/>
+        <v>23096.120000000003</v>
+      </c>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+    </row>
+    <row r="30" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+    </row>
+    <row r="31" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E31" s="4">
+        <f>ROUNDUP(D31/30,0)*2</f>
+        <v>2194</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="8">
+        <f t="shared" ref="G31:G42" si="37">SUM(D31:F31)</f>
+        <v>35096</v>
+      </c>
+      <c r="H31" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I31" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J31" s="2">
+        <f t="shared" ref="J31:J42" si="38">6%*G31</f>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K31" s="8">
+        <f t="shared" ref="K31:K42" si="39">SUM(G31:J31)</f>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <f>10%*D31</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="4">
+        <f t="shared" ref="O31:O42" si="40">SUM(L31:N31)</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P31" s="8">
+        <f t="shared" ref="P31:P42" si="41">K31+O31</f>
+        <v>44401.56</v>
+      </c>
+      <c r="Q31" s="2">
+        <v>800</v>
+      </c>
+      <c r="R31" s="2">
+        <f t="shared" ref="R31:R42" si="42">H31*2</f>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S31" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2">
+        <f t="shared" ref="U31:U42" si="43">J31*2</f>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V31" s="4">
+        <f t="shared" ref="V31:V42" si="44">SUM(Q31:U31)</f>
+        <v>17030.72</v>
+      </c>
+      <c r="W31" s="2">
+        <f t="shared" ref="W31:W42" si="45">X31+U31</f>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X31" s="10">
+        <f t="shared" ref="X31:X42" si="46">P31-V31</f>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y31" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="2">
+        <f t="shared" ref="Z31:Z42" si="47">X31-Y31</f>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+    </row>
+    <row r="32" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" ref="E32:E41" si="48">ROUNDUP(D32/30,0)*2</f>
+        <v>2194</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H32" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I32" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J32" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K32" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <f>10%*D32</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P32" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>800</v>
+      </c>
+      <c r="R32" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S32" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V32" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W32" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X32" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y32" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+    </row>
+    <row r="33" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E33" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H33" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I33" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J33" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K33" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <f>10%*D33+D33</f>
+        <v>36192.199999999997</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="4">
+        <f t="shared" si="40"/>
+        <v>36192.199999999997</v>
+      </c>
+      <c r="P33" s="8">
+        <f t="shared" si="41"/>
+        <v>77303.56</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>800</v>
+      </c>
+      <c r="R33" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S33" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V33" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W33" s="2">
+        <f t="shared" si="45"/>
+        <v>64484.359999999993</v>
+      </c>
+      <c r="X33" s="10">
+        <f t="shared" si="46"/>
+        <v>60272.84</v>
+      </c>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2">
+        <f t="shared" si="47"/>
+        <v>60272.84</v>
+      </c>
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2"/>
+    </row>
+    <row r="34" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H34" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I34" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J34" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K34" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <f>10%*D34</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P34" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>800</v>
+      </c>
+      <c r="R34" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S34" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V34" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W34" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X34" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y34" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+    </row>
+    <row r="35" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H35" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I35" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J35" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K35" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
+        <f>10%*D35</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P35" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>800</v>
+      </c>
+      <c r="R35" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S35" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V35" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W35" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X35" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y35" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2"/>
+    </row>
+    <row r="36" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H36" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I36" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J36" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K36" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2">
+        <f>10%*D36</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P36" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>800</v>
+      </c>
+      <c r="R36" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S36" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V36" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W36" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X36" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y36" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+    </row>
+    <row r="37" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E37" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H37" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I37" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J37" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K37" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
+        <f>10%*D37</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P37" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>800</v>
+      </c>
+      <c r="R37" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S37" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V37" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W37" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X37" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y37" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="2"/>
+    </row>
+    <row r="38" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H38" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I38" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J38" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K38" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <f>10%*D38</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P38" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>800</v>
+      </c>
+      <c r="R38" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S38" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V38" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W38" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X38" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y38" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2"/>
+    </row>
+    <row r="39" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E39" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H39" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I39" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J39" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K39" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <f>10%*D39</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N39" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O39" s="4">
+        <f t="shared" si="40"/>
+        <v>13290.2</v>
+      </c>
+      <c r="P39" s="8">
+        <f t="shared" si="41"/>
+        <v>54401.56</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>800</v>
+      </c>
+      <c r="R39" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S39" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V39" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W39" s="2">
+        <f t="shared" si="45"/>
+        <v>41582.359999999993</v>
+      </c>
+      <c r="X39" s="10">
+        <f t="shared" si="46"/>
+        <v>37370.839999999997</v>
+      </c>
+      <c r="Y39" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="2">
+        <f t="shared" si="47"/>
+        <v>37370.839999999997</v>
+      </c>
+      <c r="AA39" s="2"/>
+      <c r="AB39" s="2"/>
+    </row>
+    <row r="40" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H40" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I40" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J40" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K40" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <f>10%*D40</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P40" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>800</v>
+      </c>
+      <c r="R40" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S40" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V40" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W40" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X40" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y40" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA40" s="2"/>
+      <c r="AB40" s="2"/>
+    </row>
+    <row r="41" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E41" s="4">
+        <f t="shared" si="48"/>
+        <v>2194</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="8">
+        <f t="shared" si="37"/>
+        <v>35096</v>
+      </c>
+      <c r="H41" s="2">
+        <f t="shared" si="1"/>
+        <v>3509.6000000000004</v>
+      </c>
+      <c r="I41" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J41" s="2">
+        <f t="shared" si="38"/>
+        <v>2105.7599999999998</v>
+      </c>
+      <c r="K41" s="8">
+        <f t="shared" si="39"/>
+        <v>41111.360000000001</v>
+      </c>
+      <c r="L41" s="2">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2">
+        <f>10%*D41</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P41" s="8">
+        <f t="shared" si="41"/>
+        <v>44401.56</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>800</v>
+      </c>
+      <c r="R41" s="2">
+        <f t="shared" si="42"/>
+        <v>7019.2000000000007</v>
+      </c>
+      <c r="S41" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2">
+        <f t="shared" si="43"/>
+        <v>4211.5199999999995</v>
+      </c>
+      <c r="V41" s="4">
+        <f t="shared" si="44"/>
+        <v>17030.72</v>
+      </c>
+      <c r="W41" s="2">
+        <f t="shared" si="45"/>
+        <v>31582.359999999997</v>
+      </c>
+      <c r="X41" s="10">
+        <f t="shared" si="46"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="Y41" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="2">
+        <f t="shared" si="47"/>
+        <v>27370.839999999997</v>
+      </c>
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="2"/>
+    </row>
+    <row r="42" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E42" s="4">
+        <f>ROUNDUP(D42/30,0)*3</f>
+        <v>3291</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="8">
+        <f t="shared" si="37"/>
+        <v>36193</v>
+      </c>
+      <c r="H42" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I42" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J42" s="2">
+        <f t="shared" si="38"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K42" s="8">
+        <f t="shared" si="39"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2">
+        <f>10%*D42</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="4">
+        <f t="shared" si="40"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P42" s="8">
+        <f t="shared" si="41"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>800</v>
+      </c>
+      <c r="R42" s="2">
+        <f t="shared" si="42"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S42" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2">
+        <f t="shared" si="43"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V42" s="4">
+        <f t="shared" si="44"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W42" s="2">
+        <f t="shared" si="45"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X42" s="10">
+        <f t="shared" si="46"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y42" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="2">
+        <f t="shared" si="47"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+    </row>
+    <row r="43" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="8"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="2"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="2"/>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="2"/>
+    </row>
+    <row r="44" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E44" s="4">
+        <f>ROUNDUP(D44/30,0)*3</f>
+        <v>3291</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="8">
+        <f t="shared" ref="G44:G55" si="49">SUM(D44:F44)</f>
+        <v>36193</v>
+      </c>
+      <c r="H44" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I44" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J44" s="2">
+        <f t="shared" ref="J44:J55" si="50">6%*G44</f>
+        <v>2171.58</v>
+      </c>
+      <c r="K44" s="8">
+        <f t="shared" ref="K44:K55" si="51">SUM(G44:J44)</f>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L44" s="2">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2">
+        <f>10%*D44</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="4">
+        <f t="shared" ref="O44:O55" si="52">SUM(L44:N44)</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P44" s="8">
+        <f t="shared" ref="P44:P55" si="53">K44+O44</f>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>800</v>
+      </c>
+      <c r="R44" s="2">
+        <f t="shared" ref="R44:R55" si="54">H44*2</f>
+        <v>7238.6</v>
+      </c>
+      <c r="S44" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2">
+        <f t="shared" ref="U44:U55" si="55">J44*2</f>
+        <v>4343.16</v>
+      </c>
+      <c r="V44" s="4">
+        <f t="shared" ref="V44:V55" si="56">SUM(Q44:U44)</f>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W44" s="2">
+        <f t="shared" ref="W44:W55" si="57">X44+U44</f>
+        <v>32635.48</v>
+      </c>
+      <c r="X44" s="10">
+        <f t="shared" ref="X44:X55" si="58">P44-V44</f>
+        <v>28292.32</v>
+      </c>
+      <c r="Y44" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z44" s="2">
+        <f t="shared" ref="Z44:Z55" si="59">X44-Y44</f>
+        <v>28292.32</v>
+      </c>
+      <c r="AA44" s="2"/>
+      <c r="AB44" s="2"/>
+    </row>
+    <row r="45" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E45" s="4">
+        <f t="shared" ref="E45:E54" si="60">ROUNDUP(D45/30,0)*3</f>
+        <v>3291</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H45" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I45" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J45" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K45" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L45" s="2">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2">
+        <f>10%*D45</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P45" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>800</v>
+      </c>
+      <c r="R45" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S45" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V45" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W45" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X45" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y45" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z45" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA45" s="2"/>
+      <c r="AB45" s="2"/>
+    </row>
+    <row r="46" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E46" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H46" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I46" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J46" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K46" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L46" s="2">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2">
+        <f>10%*D46+D46</f>
+        <v>36192.199999999997</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="4">
+        <f t="shared" si="52"/>
+        <v>36192.199999999997</v>
+      </c>
+      <c r="P46" s="8">
+        <f t="shared" si="53"/>
+        <v>78576.08</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>800</v>
+      </c>
+      <c r="R46" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S46" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T46" s="2"/>
+      <c r="U46" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V46" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W46" s="2">
+        <f t="shared" si="57"/>
+        <v>65537.48</v>
+      </c>
+      <c r="X46" s="10">
+        <f t="shared" si="58"/>
+        <v>61194.32</v>
+      </c>
+      <c r="Y46" s="2"/>
+      <c r="Z46" s="2">
+        <f t="shared" si="59"/>
+        <v>61194.32</v>
+      </c>
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="2"/>
+    </row>
+    <row r="47" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E47" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H47" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I47" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J47" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K47" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L47" s="2">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2">
+        <f>10%*D47</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P47" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>800</v>
+      </c>
+      <c r="R47" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S47" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V47" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W47" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X47" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y47" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z47" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+    </row>
+    <row r="48" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H48" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I48" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J48" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K48" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L48" s="2">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2">
+        <f>10%*D48</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P48" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>800</v>
+      </c>
+      <c r="R48" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S48" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V48" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W48" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X48" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y48" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z48" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2"/>
+    </row>
+    <row r="49" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E49" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H49" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I49" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J49" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K49" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L49" s="2">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2">
+        <f>10%*D49</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P49" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>800</v>
+      </c>
+      <c r="R49" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S49" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T49" s="2"/>
+      <c r="U49" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V49" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W49" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X49" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y49" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z49" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA49" s="2"/>
+      <c r="AB49" s="2"/>
+    </row>
+    <row r="50" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H50" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I50" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J50" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K50" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L50" s="2">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2">
+        <f>10%*D50</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P50" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>800</v>
+      </c>
+      <c r="R50" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S50" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T50" s="2"/>
+      <c r="U50" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V50" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W50" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X50" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y50" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z50" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2"/>
+    </row>
+    <row r="51" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E51" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H51" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I51" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J51" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K51" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L51" s="2">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2">
+        <f>10%*D51</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P51" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>800</v>
+      </c>
+      <c r="R51" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S51" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V51" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W51" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X51" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y51" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z51" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="2"/>
+    </row>
+    <row r="52" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H52" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I52" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J52" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K52" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <f>10%*D52</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N52" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O52" s="4">
+        <f t="shared" si="52"/>
+        <v>13290.2</v>
+      </c>
+      <c r="P52" s="8">
+        <f t="shared" si="53"/>
+        <v>55674.080000000002</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>800</v>
+      </c>
+      <c r="R52" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S52" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V52" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W52" s="2">
+        <f t="shared" si="57"/>
+        <v>42635.479999999996</v>
+      </c>
+      <c r="X52" s="10">
+        <f t="shared" si="58"/>
+        <v>38292.32</v>
+      </c>
+      <c r="Y52" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z52" s="2">
+        <f t="shared" si="59"/>
+        <v>38292.32</v>
+      </c>
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="2"/>
+    </row>
+    <row r="53" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E53" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H53" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I53" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J53" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K53" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L53" s="2">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2">
+        <f>10%*D53</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P53" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>800</v>
+      </c>
+      <c r="R53" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S53" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V53" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W53" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X53" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y53" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z53" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA53" s="2"/>
+      <c r="AB53" s="2"/>
+    </row>
+    <row r="54" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" si="60"/>
+        <v>3291</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="8">
+        <f t="shared" si="49"/>
+        <v>36193</v>
+      </c>
+      <c r="H54" s="2">
+        <f t="shared" si="1"/>
+        <v>3619.3</v>
+      </c>
+      <c r="I54" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J54" s="2">
+        <f t="shared" si="50"/>
+        <v>2171.58</v>
+      </c>
+      <c r="K54" s="8">
+        <f t="shared" si="51"/>
+        <v>42383.880000000005</v>
+      </c>
+      <c r="L54" s="2">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2">
+        <f>10%*D54</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P54" s="8">
+        <f t="shared" si="53"/>
+        <v>45674.080000000002</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>800</v>
+      </c>
+      <c r="R54" s="2">
+        <f t="shared" si="54"/>
+        <v>7238.6</v>
+      </c>
+      <c r="S54" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2">
+        <f t="shared" si="55"/>
+        <v>4343.16</v>
+      </c>
+      <c r="V54" s="4">
+        <f t="shared" si="56"/>
+        <v>17381.760000000002</v>
+      </c>
+      <c r="W54" s="2">
+        <f t="shared" si="57"/>
+        <v>32635.48</v>
+      </c>
+      <c r="X54" s="10">
+        <f t="shared" si="58"/>
+        <v>28292.32</v>
+      </c>
+      <c r="Y54" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z54" s="2">
+        <f t="shared" si="59"/>
+        <v>28292.32</v>
+      </c>
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="2"/>
+    </row>
+    <row r="55" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E55" s="4">
+        <f t="shared" ref="E45:E68" si="61">ROUNDUP(D55/30,0)*4</f>
+        <v>4388</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="8">
+        <f t="shared" si="49"/>
+        <v>37290</v>
+      </c>
+      <c r="H55" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I55" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J55" s="2">
+        <f t="shared" si="50"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K55" s="8">
+        <f t="shared" si="51"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L55" s="2">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2">
+        <f>10%*D55</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="4">
+        <f t="shared" si="52"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P55" s="8">
+        <f t="shared" si="53"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>800</v>
+      </c>
+      <c r="R55" s="2">
+        <f t="shared" si="54"/>
+        <v>7458</v>
+      </c>
+      <c r="S55" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T55" s="2"/>
+      <c r="U55" s="2">
+        <f t="shared" si="55"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V55" s="4">
+        <f t="shared" si="56"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W55" s="2">
+        <f t="shared" si="57"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X55" s="10">
+        <f t="shared" si="58"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y55" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z55" s="2">
+        <f t="shared" si="59"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA55" s="2"/>
+      <c r="AB55" s="2"/>
+    </row>
+    <row r="56" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="10"/>
+      <c r="Y56" s="2"/>
+      <c r="Z56" s="2"/>
+      <c r="AA56" s="2"/>
+      <c r="AB56" s="2"/>
+    </row>
+    <row r="57" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E57" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="8">
+        <f t="shared" ref="G57:G68" si="62">SUM(D57:F57)</f>
+        <v>37290</v>
+      </c>
+      <c r="H57" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I57" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J57" s="2">
+        <f t="shared" ref="J57:J68" si="63">6%*G57</f>
+        <v>2237.4</v>
+      </c>
+      <c r="K57" s="8">
+        <f t="shared" ref="K57:K68" si="64">SUM(G57:J57)</f>
+        <v>43656.4</v>
+      </c>
+      <c r="L57" s="2">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2">
+        <f>10%*D57</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="4">
+        <f t="shared" ref="O57:O68" si="65">SUM(L57:N57)</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P57" s="8">
+        <f t="shared" ref="P57:P68" si="66">K57+O57</f>
+        <v>46946.6</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>800</v>
+      </c>
+      <c r="R57" s="2">
+        <f t="shared" ref="R57:R68" si="67">H57*2</f>
+        <v>7458</v>
+      </c>
+      <c r="S57" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T57" s="2"/>
+      <c r="U57" s="2">
+        <f t="shared" ref="U57:U68" si="68">J57*2</f>
+        <v>4474.8</v>
+      </c>
+      <c r="V57" s="4">
+        <f t="shared" ref="V57:V68" si="69">SUM(Q57:U57)</f>
+        <v>17732.8</v>
+      </c>
+      <c r="W57" s="2">
+        <f t="shared" ref="W57:W68" si="70">X57+U57</f>
+        <v>33688.6</v>
+      </c>
+      <c r="X57" s="10">
+        <f t="shared" ref="X57:X68" si="71">P57-V57</f>
+        <v>29213.8</v>
+      </c>
+      <c r="Y57" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z57" s="2">
+        <f t="shared" ref="Z57:Z68" si="72">X57-Y57</f>
+        <v>29213.8</v>
+      </c>
+      <c r="AA57" s="2"/>
+      <c r="AB57" s="2"/>
+    </row>
+    <row r="58" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E58" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H58" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I58" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J58" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K58" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L58" s="2">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2">
+        <f>10%*D58</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P58" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>800</v>
+      </c>
+      <c r="R58" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S58" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V58" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W58" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X58" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y58" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z58" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA58" s="2"/>
+      <c r="AB58" s="2"/>
+    </row>
+    <row r="59" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E59" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H59" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I59" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J59" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K59" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L59" s="2">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2">
+        <f>10%*D59+D59</f>
+        <v>36192.199999999997</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="4">
+        <f t="shared" si="65"/>
+        <v>36192.199999999997</v>
+      </c>
+      <c r="P59" s="8">
+        <f t="shared" si="66"/>
+        <v>79848.600000000006</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>800</v>
+      </c>
+      <c r="R59" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S59" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T59" s="2"/>
+      <c r="U59" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V59" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W59" s="2">
+        <f t="shared" si="70"/>
+        <v>66590.600000000006</v>
+      </c>
+      <c r="X59" s="10">
+        <f t="shared" si="71"/>
+        <v>62115.8</v>
+      </c>
+      <c r="Y59" s="2"/>
+      <c r="Z59" s="2">
+        <f t="shared" si="72"/>
+        <v>62115.8</v>
+      </c>
+      <c r="AA59" s="2"/>
+      <c r="AB59" s="2"/>
+    </row>
+    <row r="60" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E60" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H60" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I60" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J60" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K60" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L60" s="2">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2">
+        <f>10%*D60</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P60" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>800</v>
+      </c>
+      <c r="R60" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S60" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T60" s="2"/>
+      <c r="U60" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V60" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W60" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X60" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y60" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z60" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA60" s="2"/>
+      <c r="AB60" s="2"/>
+    </row>
+    <row r="61" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E61" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H61" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I61" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J61" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K61" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L61" s="2">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2">
+        <f>10%*D61</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P61" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>800</v>
+      </c>
+      <c r="R61" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S61" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V61" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W61" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X61" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y61" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z61" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA61" s="2"/>
+      <c r="AB61" s="2"/>
+    </row>
+    <row r="62" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E62" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H62" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I62" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J62" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K62" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L62" s="2">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2">
+        <f>10%*D62</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P62" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>800</v>
+      </c>
+      <c r="R62" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S62" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V62" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W62" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X62" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y62" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z62" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA62" s="2"/>
+      <c r="AB62" s="2"/>
+    </row>
+    <row r="63" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E63" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H63" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I63" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J63" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K63" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L63" s="2">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2">
+        <f>10%*D63</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P63" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>800</v>
+      </c>
+      <c r="R63" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S63" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V63" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W63" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X63" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y63" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z63" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA63" s="2"/>
+      <c r="AB63" s="2"/>
+    </row>
+    <row r="64" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E64" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H64" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I64" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J64" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K64" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L64" s="2">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2">
+        <f>10%*D64</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P64" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>800</v>
+      </c>
+      <c r="R64" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S64" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T64" s="2"/>
+      <c r="U64" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V64" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W64" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X64" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y64" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z64" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA64" s="2"/>
+      <c r="AB64" s="2"/>
+    </row>
+    <row r="65" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E65" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H65" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I65" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J65" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K65" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L65" s="2">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2">
+        <f>10%*D65</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N65" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O65" s="4">
+        <f t="shared" si="65"/>
+        <v>13290.2</v>
+      </c>
+      <c r="P65" s="8">
+        <f t="shared" si="66"/>
+        <v>56946.600000000006</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>800</v>
+      </c>
+      <c r="R65" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S65" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V65" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W65" s="2">
+        <f t="shared" si="70"/>
+        <v>43688.600000000006</v>
+      </c>
+      <c r="X65" s="10">
+        <f t="shared" si="71"/>
+        <v>39213.800000000003</v>
+      </c>
+      <c r="Y65" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z65" s="2">
+        <f t="shared" si="72"/>
+        <v>39213.800000000003</v>
+      </c>
+      <c r="AA65" s="2"/>
+      <c r="AB65" s="2"/>
+    </row>
+    <row r="66" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E66" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H66" s="2">
+        <f t="shared" si="1"/>
+        <v>3729</v>
+      </c>
+      <c r="I66" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J66" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K66" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L66" s="2">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2">
+        <f>10%*D66</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P66" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>800</v>
+      </c>
+      <c r="R66" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S66" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T66" s="2"/>
+      <c r="U66" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V66" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W66" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X66" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y66" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z66" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA66" s="2"/>
+      <c r="AB66" s="2"/>
+    </row>
+    <row r="67" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E67" s="4">
+        <f t="shared" si="61"/>
+        <v>4388</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="8">
+        <f t="shared" si="62"/>
+        <v>37290</v>
+      </c>
+      <c r="H67" s="2">
+        <f t="shared" ref="H67:H68" si="73">10%*G67</f>
+        <v>3729</v>
+      </c>
+      <c r="I67" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J67" s="2">
+        <f t="shared" si="63"/>
+        <v>2237.4</v>
+      </c>
+      <c r="K67" s="8">
+        <f t="shared" si="64"/>
+        <v>43656.4</v>
+      </c>
+      <c r="L67" s="2">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2">
+        <f>10%*D67</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P67" s="8">
+        <f t="shared" si="66"/>
+        <v>46946.6</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>800</v>
+      </c>
+      <c r="R67" s="2">
+        <f t="shared" si="67"/>
+        <v>7458</v>
+      </c>
+      <c r="S67" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T67" s="2"/>
+      <c r="U67" s="2">
+        <f t="shared" si="68"/>
+        <v>4474.8</v>
+      </c>
+      <c r="V67" s="4">
+        <f t="shared" si="69"/>
+        <v>17732.8</v>
+      </c>
+      <c r="W67" s="2">
+        <f t="shared" si="70"/>
+        <v>33688.6</v>
+      </c>
+      <c r="X67" s="10">
+        <f t="shared" si="71"/>
+        <v>29213.8</v>
+      </c>
+      <c r="Y67" s="2">
+        <f t="shared" ref="Y67:Y68" si="74">IF(X67*13&gt;600000,1%*X67,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z67" s="2">
+        <f t="shared" si="72"/>
+        <v>29213.8</v>
+      </c>
+      <c r="AA67" s="2"/>
+      <c r="AB67" s="2"/>
+    </row>
+    <row r="68" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E68" s="4">
+        <f>ROUNDUP(D68/30,0)*5</f>
+        <v>5485</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="8">
+        <f t="shared" si="62"/>
+        <v>38387</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" si="73"/>
+        <v>3838.7000000000003</v>
+      </c>
+      <c r="I68" s="2">
+        <f>400</f>
+        <v>400</v>
+      </c>
+      <c r="J68" s="2">
+        <f t="shared" si="63"/>
+        <v>2303.2199999999998</v>
+      </c>
+      <c r="K68" s="8">
+        <f t="shared" si="64"/>
+        <v>44928.92</v>
+      </c>
+      <c r="L68" s="2">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2">
+        <f>10%*D68</f>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="4">
+        <f t="shared" si="65"/>
+        <v>3290.2000000000003</v>
+      </c>
+      <c r="P68" s="8">
+        <f t="shared" si="66"/>
+        <v>48219.119999999995</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>800</v>
+      </c>
+      <c r="R68" s="2">
+        <f t="shared" si="67"/>
+        <v>7677.4000000000005</v>
+      </c>
+      <c r="S68" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2">
+        <f t="shared" si="68"/>
+        <v>4606.4399999999996</v>
+      </c>
+      <c r="V68" s="4">
+        <f t="shared" si="69"/>
+        <v>18083.84</v>
+      </c>
+      <c r="W68" s="2">
+        <f t="shared" si="70"/>
+        <v>34741.719999999994</v>
+      </c>
+      <c r="X68" s="10">
+        <f t="shared" si="71"/>
+        <v>30135.279999999995</v>
+      </c>
+      <c r="Y68" s="2">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
+      <c r="Z68" s="2">
+        <f t="shared" si="72"/>
+        <v>30135.279999999995</v>
+      </c>
+      <c r="AA68" s="2"/>
+      <c r="AB68" s="2"/>
+    </row>
+    <row r="69" spans="1:28" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="8"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="2"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="2"/>
+      <c r="X69" s="10"/>
+      <c r="Y69" s="2"/>
+      <c r="Z69" s="2"/>
+      <c r="AA69" s="2"/>
+      <c r="AB69" s="2"/>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="4">
+        <v>32902</v>
+      </c>
+      <c r="E70" s="4">
+        <f>ROUNDUP(D70/30,0)*4</f>
+        <v>4388</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="8">
+        <f>SUM(D70:F70)</f>
+        <v>37290</v>
+      </c>
+      <c r="H70" s="2">
+        <f>10%*G70</f>
+        <v>3729</v>
+      </c>
+      <c r="I70" s="2">
+        <v>400</v>
+      </c>
+      <c r="J70" s="2">
+        <f>6%*G70</f>
+        <v>2237.4</v>
+      </c>
+      <c r="K70" s="8">
+        <f>SUM(G70:J70)</f>
+        <v>43656.4</v>
+      </c>
+      <c r="L70" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M70" s="2">
+        <v>0</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="4">
+        <f>SUM(L70:M70)</f>
+        <v>2000</v>
+      </c>
+      <c r="P70" s="8">
+        <f>K70+O70</f>
+        <v>45656.4</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>800</v>
+      </c>
+      <c r="R70" s="2">
+        <f>H70*2</f>
+        <v>7458</v>
+      </c>
+      <c r="S70" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2">
+        <f>J70*2</f>
+        <v>4474.8</v>
+      </c>
+      <c r="V70" s="4">
+        <f>SUM(Q70:U70)</f>
+        <v>17732.8</v>
+      </c>
+      <c r="W70" s="2">
+        <f>X70+U70</f>
+        <v>32398.400000000001</v>
+      </c>
+      <c r="X70" s="10">
+        <f>P70-V70</f>
+        <v>27923.600000000002</v>
+      </c>
+      <c r="Y70" s="2">
+        <f>IF(X70*13&gt;600000,1%*X70,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z70" s="2">
+        <f>X70-Y70</f>
+        <v>27923.600000000002</v>
+      </c>
+      <c r="AA70" s="2"/>
+      <c r="AB70" s="2"/>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E71" s="4">
+        <f>ROUNDUP(D71/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="8">
+        <f>SUM(D71:F71)</f>
+        <v>39362</v>
+      </c>
+      <c r="H71" s="2">
+        <f>10%*G71</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I71" s="2">
+        <v>400</v>
+      </c>
+      <c r="J71" s="2">
+        <f>6%*G71</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K71" s="8">
+        <f>SUM(G71:J71)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L71" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M71" s="2">
+        <f>G71</f>
+        <v>39362</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="4">
+        <f>SUM(L71:M71)</f>
+        <v>44362</v>
+      </c>
+      <c r="P71" s="8">
+        <f>K71+O71</f>
+        <v>90421.92</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>800</v>
+      </c>
+      <c r="R71" s="2">
+        <f>H71*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S71" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T71" s="2"/>
+      <c r="U71" s="2">
+        <f>J71*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V71" s="4">
+        <f>SUM(Q71:U71)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W71" s="2">
+        <f>X71+U71</f>
+        <v>76749.52</v>
+      </c>
+      <c r="X71" s="10">
+        <f>P71-V71</f>
+        <v>72026.080000000002</v>
+      </c>
+      <c r="Y71" s="12">
+        <f>IF(X71*13&gt;600000,1%*X71,0)</f>
+        <v>720.26080000000002</v>
+      </c>
+      <c r="Z71" s="12">
+        <f>X71-Y71</f>
+        <v>71305.819199999998</v>
+      </c>
+      <c r="AA71" s="2"/>
+      <c r="AB71" s="2"/>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E72" s="4">
+        <f>ROUNDUP(D72/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F72" s="2"/>
+      <c r="G72" s="8">
+        <f>SUM(D72:F72)</f>
+        <v>39362</v>
+      </c>
+      <c r="H72" s="2">
+        <f>10%*G72</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I72" s="2">
+        <v>400</v>
+      </c>
+      <c r="J72" s="2">
+        <f>6%*G72</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K72" s="8">
+        <f>SUM(G72:J72)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L72" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M72" s="2">
+        <v>0</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="4">
+        <f>SUM(L72:M72)</f>
+        <v>5000</v>
+      </c>
+      <c r="P72" s="8">
+        <f>K72+O72</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>800</v>
+      </c>
+      <c r="R72" s="2">
+        <f>H72*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S72" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2">
+        <f>J72*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V72" s="4">
+        <f>SUM(Q72:U72)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W72" s="2">
+        <f>X72+U72</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X72" s="10">
+        <f>P72-V72</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y72" s="2">
+        <f>IF(X72*13&gt;600000,1%*X72,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z72" s="2">
+        <f>X72-Y72</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA72" s="2"/>
+      <c r="AB72" s="2"/>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E73" s="4">
+        <f>ROUNDUP(D73/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F73" s="2"/>
+      <c r="G73" s="8">
+        <f>SUM(D73:F73)</f>
+        <v>39362</v>
+      </c>
+      <c r="H73" s="2">
+        <f>10%*G73</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I73" s="2">
+        <v>400</v>
+      </c>
+      <c r="J73" s="2">
+        <f>6%*G73</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K73" s="8">
+        <f>SUM(G73:J73)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L73" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="4">
+        <f>SUM(L73:M73)</f>
+        <v>5000</v>
+      </c>
+      <c r="P73" s="8">
+        <f>K73+O73</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>800</v>
+      </c>
+      <c r="R73" s="2">
+        <f>H73*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S73" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T73" s="2"/>
+      <c r="U73" s="2">
+        <f>J73*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V73" s="4">
+        <f>SUM(Q73:U73)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W73" s="2">
+        <f>X73+U73</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X73" s="10">
+        <f>P73-V73</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y73" s="2">
+        <f>IF(X73*13&gt;600000,1%*X73,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z73" s="2">
+        <f>X73-Y73</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA73" s="2"/>
+      <c r="AB73" s="2"/>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E74" s="4">
+        <f>ROUNDUP(D74/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="8">
+        <f>SUM(D74:F74)</f>
+        <v>39362</v>
+      </c>
+      <c r="H74" s="2">
+        <f>10%*G74</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I74" s="2">
+        <v>400</v>
+      </c>
+      <c r="J74" s="2">
+        <f>6%*G74</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K74" s="8">
+        <f>SUM(G74:J74)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L74" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M74" s="2">
+        <v>0</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="4">
+        <f>SUM(L74:M74)</f>
+        <v>5000</v>
+      </c>
+      <c r="P74" s="8">
+        <f>K74+O74</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>800</v>
+      </c>
+      <c r="R74" s="2">
+        <f>H74*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S74" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T74" s="2"/>
+      <c r="U74" s="2">
+        <f>J74*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V74" s="4">
+        <f>SUM(Q74:U74)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W74" s="2">
+        <f>X74+U74</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X74" s="10">
+        <f>P74-V74</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y74" s="2">
+        <f>IF(X74*13&gt;600000,1%*X74,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z74" s="2">
+        <f>X74-Y74</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA74" s="2"/>
+      <c r="AB74" s="2"/>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E75" s="4">
+        <f t="shared" ref="E75:E80" si="75">ROUNDUP(D75/30,0)*4</f>
+        <v>4632</v>
+      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="8">
+        <f t="shared" ref="G75:G81" si="76">SUM(D75:F75)</f>
+        <v>39362</v>
+      </c>
+      <c r="H75" s="2">
+        <f t="shared" ref="H75:H81" si="77">10%*G75</f>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I75" s="2">
+        <v>400</v>
+      </c>
+      <c r="J75" s="2">
+        <f t="shared" ref="J75:J81" si="78">6%*G75</f>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K75" s="8">
+        <f t="shared" ref="K75:K81" si="79">SUM(G75:J75)</f>
+        <v>46059.92</v>
+      </c>
+      <c r="L75" s="2">
+        <f t="shared" ref="L75:L84" si="80">2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M75" s="2">
+        <v>0</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="4">
+        <f t="shared" ref="O75:O77" si="81">SUM(L75:M75)</f>
+        <v>5000</v>
+      </c>
+      <c r="P75" s="8">
+        <f t="shared" ref="P75:P81" si="82">K75+O75</f>
+        <v>51059.92</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>800</v>
+      </c>
+      <c r="R75" s="2">
+        <f t="shared" ref="R75:R81" si="83">H75*2</f>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S75" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T75" s="2"/>
+      <c r="U75" s="2">
+        <f t="shared" ref="U75:U81" si="84">J75*2</f>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V75" s="4">
+        <f t="shared" ref="V75:V81" si="85">SUM(Q75:U75)</f>
+        <v>18395.84</v>
+      </c>
+      <c r="W75" s="2">
+        <f t="shared" ref="W75:W81" si="86">X75+U75</f>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X75" s="10">
+        <f t="shared" ref="X75:X81" si="87">P75-V75</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y75" s="2">
+        <f t="shared" ref="Y75:Y81" si="88">IF(X75*13&gt;600000,1%*X75,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z75" s="2">
+        <f t="shared" ref="Z75:Z81" si="89">X75-Y75</f>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA75" s="2"/>
+      <c r="AB75" s="2"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E76" s="4">
+        <f t="shared" si="75"/>
+        <v>4632</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="8">
+        <f t="shared" si="76"/>
+        <v>39362</v>
+      </c>
+      <c r="H76" s="2">
+        <f t="shared" si="77"/>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I76" s="2">
+        <v>400</v>
+      </c>
+      <c r="J76" s="2">
+        <f t="shared" si="78"/>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K76" s="8">
+        <f t="shared" si="79"/>
+        <v>46059.92</v>
+      </c>
+      <c r="L76" s="2">
+        <f t="shared" si="80"/>
+        <v>5000</v>
+      </c>
+      <c r="M76" s="2">
+        <v>0</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="4">
+        <f t="shared" si="81"/>
+        <v>5000</v>
+      </c>
+      <c r="P76" s="8">
+        <f t="shared" si="82"/>
+        <v>51059.92</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>800</v>
+      </c>
+      <c r="R76" s="2">
+        <f t="shared" si="83"/>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S76" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T76" s="2"/>
+      <c r="U76" s="2">
+        <f t="shared" si="84"/>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V76" s="4">
+        <f t="shared" si="85"/>
+        <v>18395.84</v>
+      </c>
+      <c r="W76" s="2">
+        <f t="shared" si="86"/>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X76" s="10">
+        <f t="shared" si="87"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y76" s="2">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="Z76" s="2">
+        <f t="shared" si="89"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA76" s="2"/>
+      <c r="AB76" s="2"/>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E77" s="4">
+        <f t="shared" si="75"/>
+        <v>4632</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" s="8">
+        <f t="shared" si="76"/>
+        <v>39362</v>
+      </c>
+      <c r="H77" s="2">
+        <f t="shared" si="77"/>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I77" s="2">
+        <v>400</v>
+      </c>
+      <c r="J77" s="2">
+        <f t="shared" si="78"/>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K77" s="8">
+        <f t="shared" si="79"/>
+        <v>46059.92</v>
+      </c>
+      <c r="L77" s="2">
+        <f t="shared" si="80"/>
+        <v>5000</v>
+      </c>
+      <c r="M77" s="2">
+        <v>0</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="4">
+        <f t="shared" si="81"/>
+        <v>5000</v>
+      </c>
+      <c r="P77" s="8">
+        <f t="shared" si="82"/>
+        <v>51059.92</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>800</v>
+      </c>
+      <c r="R77" s="2">
+        <f t="shared" si="83"/>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S77" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T77" s="2"/>
+      <c r="U77" s="2">
+        <f t="shared" si="84"/>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V77" s="4">
+        <f t="shared" si="85"/>
+        <v>18395.84</v>
+      </c>
+      <c r="W77" s="2">
+        <f t="shared" si="86"/>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X77" s="10">
+        <f t="shared" si="87"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y77" s="2">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="Z77" s="2">
+        <f t="shared" si="89"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA77" s="2"/>
+      <c r="AB77" s="2"/>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E78" s="4">
+        <f t="shared" si="75"/>
+        <v>4632</v>
+      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" s="8">
+        <f t="shared" si="76"/>
+        <v>39362</v>
+      </c>
+      <c r="H78" s="2">
+        <f t="shared" si="77"/>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I78" s="2">
+        <v>400</v>
+      </c>
+      <c r="J78" s="2">
+        <f t="shared" si="78"/>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K78" s="8">
+        <f t="shared" si="79"/>
+        <v>46059.92</v>
+      </c>
+      <c r="L78" s="2">
+        <f t="shared" si="80"/>
+        <v>5000</v>
+      </c>
+      <c r="M78" s="2">
+        <v>0</v>
+      </c>
+      <c r="N78" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O78" s="4">
+        <f>SUM(L78:N78)</f>
+        <v>15000</v>
+      </c>
+      <c r="P78" s="8">
+        <f t="shared" si="82"/>
+        <v>61059.92</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>800</v>
+      </c>
+      <c r="R78" s="2">
+        <f t="shared" si="83"/>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S78" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T78" s="2"/>
+      <c r="U78" s="2">
+        <f t="shared" si="84"/>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V78" s="4">
+        <f t="shared" si="85"/>
+        <v>18395.84</v>
+      </c>
+      <c r="W78" s="2">
+        <f t="shared" si="86"/>
+        <v>47387.520000000004</v>
+      </c>
+      <c r="X78" s="10">
+        <f t="shared" si="87"/>
+        <v>42664.08</v>
+      </c>
+      <c r="Y78" s="2">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="2">
+        <f t="shared" si="89"/>
+        <v>42664.08</v>
+      </c>
+      <c r="AA78" s="2"/>
+      <c r="AB78" s="2"/>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E79" s="4">
+        <f t="shared" si="75"/>
+        <v>4632</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="8">
+        <f t="shared" si="76"/>
+        <v>39362</v>
+      </c>
+      <c r="H79" s="2">
+        <f t="shared" si="77"/>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I79" s="2">
+        <v>400</v>
+      </c>
+      <c r="J79" s="2">
+        <f t="shared" si="78"/>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K79" s="8">
+        <f t="shared" si="79"/>
+        <v>46059.92</v>
+      </c>
+      <c r="L79" s="2">
+        <f t="shared" si="80"/>
+        <v>5000</v>
+      </c>
+      <c r="M79" s="2">
+        <v>0</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="4">
+        <f t="shared" ref="O79:O81" si="90">SUM(L79:M79)</f>
+        <v>5000</v>
+      </c>
+      <c r="P79" s="8">
+        <f t="shared" si="82"/>
+        <v>51059.92</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>800</v>
+      </c>
+      <c r="R79" s="2">
+        <f t="shared" si="83"/>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S79" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T79" s="2"/>
+      <c r="U79" s="2">
+        <f t="shared" si="84"/>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V79" s="4">
+        <f t="shared" si="85"/>
+        <v>18395.84</v>
+      </c>
+      <c r="W79" s="2">
+        <f t="shared" si="86"/>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X79" s="10">
+        <f t="shared" si="87"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y79" s="2">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="Z79" s="2">
+        <f t="shared" si="89"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA79" s="2"/>
+      <c r="AB79" s="2"/>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E80" s="4">
+        <f t="shared" si="75"/>
+        <v>4632</v>
+      </c>
+      <c r="F80" s="2"/>
+      <c r="G80" s="8">
+        <f t="shared" si="76"/>
+        <v>39362</v>
+      </c>
+      <c r="H80" s="2">
+        <f t="shared" si="77"/>
+        <v>3936.2000000000003</v>
+      </c>
+      <c r="I80" s="2">
+        <v>400</v>
+      </c>
+      <c r="J80" s="2">
+        <f t="shared" si="78"/>
+        <v>2361.7199999999998</v>
+      </c>
+      <c r="K80" s="8">
+        <f t="shared" si="79"/>
+        <v>46059.92</v>
+      </c>
+      <c r="L80" s="2">
+        <f t="shared" si="80"/>
+        <v>5000</v>
+      </c>
+      <c r="M80" s="2">
+        <v>0</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="4">
+        <f t="shared" si="90"/>
+        <v>5000</v>
+      </c>
+      <c r="P80" s="8">
+        <f t="shared" si="82"/>
+        <v>51059.92</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>800</v>
+      </c>
+      <c r="R80" s="2">
+        <f t="shared" si="83"/>
+        <v>7872.4000000000005</v>
+      </c>
+      <c r="S80" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T80" s="2"/>
+      <c r="U80" s="2">
+        <f t="shared" si="84"/>
+        <v>4723.4399999999996</v>
+      </c>
+      <c r="V80" s="4">
+        <f t="shared" si="85"/>
+        <v>18395.84</v>
+      </c>
+      <c r="W80" s="2">
+        <f t="shared" si="86"/>
+        <v>37387.519999999997</v>
+      </c>
+      <c r="X80" s="10">
+        <f t="shared" si="87"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="Y80" s="2">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="Z80" s="2">
+        <f t="shared" si="89"/>
+        <v>32664.079999999998</v>
+      </c>
+      <c r="AA80" s="2"/>
+      <c r="AB80" s="2"/>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="4">
+        <v>34730</v>
+      </c>
+      <c r="E81" s="4">
+        <f>ROUNDUP(D81/30,0)*5</f>
+        <v>5790</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" s="8">
+        <f t="shared" si="76"/>
+        <v>40520</v>
+      </c>
+      <c r="H81" s="2">
+        <f t="shared" si="77"/>
+        <v>4052</v>
+      </c>
+      <c r="I81" s="2">
+        <v>400</v>
+      </c>
+      <c r="J81" s="2">
+        <f t="shared" si="78"/>
+        <v>2431.1999999999998</v>
+      </c>
+      <c r="K81" s="8">
+        <f t="shared" si="79"/>
+        <v>47403.199999999997</v>
+      </c>
+      <c r="L81" s="2">
+        <f t="shared" si="80"/>
+        <v>5000</v>
+      </c>
+      <c r="M81" s="2">
+        <v>0</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="4">
+        <f t="shared" si="90"/>
+        <v>5000</v>
+      </c>
+      <c r="P81" s="8">
+        <f t="shared" si="82"/>
+        <v>52403.199999999997</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>800</v>
+      </c>
+      <c r="R81" s="2">
+        <f t="shared" si="83"/>
+        <v>8104</v>
+      </c>
+      <c r="S81" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T81" s="2"/>
+      <c r="U81" s="2">
+        <f t="shared" si="84"/>
+        <v>4862.3999999999996</v>
+      </c>
+      <c r="V81" s="4">
+        <f t="shared" si="85"/>
+        <v>18766.400000000001</v>
+      </c>
+      <c r="W81" s="2">
+        <f t="shared" si="86"/>
+        <v>38499.199999999997</v>
+      </c>
+      <c r="X81" s="10">
+        <f t="shared" si="87"/>
+        <v>33636.799999999996</v>
+      </c>
+      <c r="Y81" s="2">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="Z81" s="2">
+        <f t="shared" si="89"/>
+        <v>33636.799999999996</v>
+      </c>
+      <c r="AA81" s="2"/>
+      <c r="AB81" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="8">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2">
+        <v>5100</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="8"/>
+      <c r="Q82" s="2"/>
+      <c r="R82" s="2"/>
+      <c r="S82" s="2"/>
+      <c r="T82" s="2"/>
+      <c r="U82" s="2"/>
+      <c r="V82" s="4"/>
+      <c r="W82" s="2"/>
+      <c r="X82" s="10"/>
+      <c r="Y82" s="2"/>
+      <c r="Z82" s="2"/>
+      <c r="AA82" s="2"/>
+      <c r="AB82" s="2"/>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="8"/>
+      <c r="Q83" s="2"/>
+      <c r="R83" s="2"/>
+      <c r="S83" s="2"/>
+      <c r="T83" s="2"/>
+      <c r="U83" s="2"/>
+      <c r="V83" s="4"/>
+      <c r="W83" s="2"/>
+      <c r="X83" s="10"/>
+      <c r="Y83" s="2"/>
+      <c r="Z83" s="2"/>
+      <c r="AA83" s="2"/>
+      <c r="AB83" s="2"/>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="4">
+        <f>34730*1.1</f>
+        <v>38203</v>
+      </c>
+      <c r="E84" s="4">
+        <f>ROUNDUP(D84/30,0)*4</f>
+        <v>5096</v>
+      </c>
+      <c r="F84" s="2"/>
+      <c r="G84" s="8">
+        <f t="shared" ref="G84" si="91">SUM(D84:F84)</f>
+        <v>43299</v>
+      </c>
+      <c r="H84" s="2">
+        <f t="shared" ref="H84" si="92">10%*G84</f>
+        <v>4329.9000000000005</v>
+      </c>
+      <c r="I84" s="2">
+        <v>400</v>
+      </c>
+      <c r="J84" s="2">
+        <f t="shared" ref="J84" si="93">6%*G84</f>
+        <v>2597.94</v>
+      </c>
+      <c r="K84" s="8">
+        <f t="shared" ref="K84" si="94">SUM(G84:J84)</f>
+        <v>50626.840000000004</v>
+      </c>
+      <c r="L84" s="2">
+        <f t="shared" si="80"/>
+        <v>5000</v>
+      </c>
+      <c r="M84" s="2">
+        <f>10%*D84</f>
+        <v>3820.3</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="4">
+        <f t="shared" ref="O84" si="95">SUM(L84:M84)</f>
+        <v>8820.2999999999993</v>
+      </c>
+      <c r="P84" s="8">
+        <f t="shared" ref="P84" si="96">K84+O84</f>
+        <v>59447.14</v>
+      </c>
+      <c r="Q84" s="2">
+        <v>800</v>
+      </c>
+      <c r="R84" s="2">
+        <f t="shared" ref="R84" si="97">H84*2</f>
+        <v>8659.8000000000011</v>
+      </c>
+      <c r="S84" s="2">
+        <v>5000</v>
+      </c>
+      <c r="T84" s="2"/>
+      <c r="U84" s="2">
+        <f t="shared" ref="U84" si="98">J84*2</f>
+        <v>5195.88</v>
+      </c>
+      <c r="V84" s="4">
+        <f t="shared" ref="V84" si="99">SUM(Q84:U84)</f>
+        <v>19655.68</v>
+      </c>
+      <c r="W84" s="2">
+        <f t="shared" ref="W84" si="100">X84+U84</f>
+        <v>44987.34</v>
+      </c>
+      <c r="X84" s="10">
+        <f t="shared" ref="X84" si="101">P84-V84</f>
+        <v>39791.46</v>
+      </c>
+      <c r="Y84" s="2">
+        <f t="shared" ref="Y84" si="102">IF(X84*13&gt;600000,1%*X84,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z84" s="2">
+        <f t="shared" ref="Z84" si="103">X84-Y84</f>
+        <v>39791.46</v>
+      </c>
+      <c r="AA84" s="2"/>
+      <c r="AB84" s="2"/>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="8"/>
+      <c r="Q85" s="2"/>
+      <c r="R85" s="2"/>
+      <c r="S85" s="2"/>
+      <c r="T85" s="2"/>
+      <c r="U85" s="2"/>
+      <c r="V85" s="4"/>
+      <c r="W85" s="2"/>
+      <c r="X85" s="10"/>
+      <c r="Y85" s="2"/>
+      <c r="Z85" s="2"/>
+      <c r="AA85" s="2"/>
+      <c r="AB85" s="2"/>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="4">
+        <v>43689</v>
+      </c>
+      <c r="E86" s="4">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="8">
+        <f>SUM(D86:F86)</f>
+        <v>43689</v>
+      </c>
+      <c r="H86" s="2">
+        <f>10%*G86</f>
+        <v>4368.9000000000005</v>
+      </c>
+      <c r="I86" s="2">
+        <v>400</v>
+      </c>
+      <c r="J86" s="2">
+        <f>6%*G86</f>
+        <v>2621.3399999999997</v>
+      </c>
+      <c r="K86" s="8">
+        <f>SUM(G86:J86)</f>
+        <v>51079.24</v>
+      </c>
+      <c r="L86" s="2">
+        <f>2000+3000</f>
+        <v>5000</v>
+      </c>
+      <c r="M86" s="2">
+        <v>0</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="4">
+        <f>SUM(L86:M86)</f>
+        <v>5000</v>
+      </c>
+      <c r="P86" s="8">
+        <f>K86+O86</f>
+        <v>56079.24</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>801</v>
+      </c>
+      <c r="R86" s="2">
+        <f>H86*2</f>
+        <v>8737.8000000000011</v>
+      </c>
+      <c r="S86" s="2">
+        <v>1000</v>
+      </c>
+      <c r="T86" s="2"/>
+      <c r="U86" s="2">
+        <f>J86*2</f>
+        <v>5242.6799999999994</v>
+      </c>
+      <c r="V86" s="4">
+        <f>SUM(Q86:U86)</f>
+        <v>15781.48</v>
+      </c>
+      <c r="W86" s="2">
+        <f>X86+U86</f>
+        <v>45540.439999999995</v>
+      </c>
+      <c r="X86" s="10">
+        <f>P86-V86</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="Y86" s="2">
+        <f>IF(X86*13&gt;600000,1%*X86,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z86" s="2">
+        <f>X86-Y86</f>
+        <v>40297.759999999995</v>
+      </c>
+      <c r="AA86" s="2"/>
+      <c r="AB86" s="2"/>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="8"/>
+      <c r="Q87" s="2"/>
+      <c r="R87" s="2"/>
+      <c r="S87" s="2"/>
+      <c r="T87" s="2"/>
+      <c r="U87" s="2"/>
+      <c r="V87" s="4"/>
+      <c r="W87" s="2"/>
+      <c r="X87" s="10"/>
+      <c r="Y87" s="2"/>
+      <c r="Z87" s="2"/>
+      <c r="AA87" s="2"/>
+      <c r="AB87" s="2"/>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="8"/>
+      <c r="Q88" s="2"/>
+      <c r="R88" s="2"/>
+      <c r="S88" s="2"/>
+      <c r="T88" s="2"/>
+      <c r="U88" s="2"/>
+      <c r="V88" s="4"/>
+      <c r="W88" s="2"/>
+      <c r="X88" s="8">
+        <f>SUM(X3:X81)</f>
+        <v>2186834.9200000013</v>
+      </c>
+      <c r="Y88" s="2"/>
+      <c r="Z88" s="2"/>
+      <c r="AA88" s="2"/>
+      <c r="AB88" s="2"/>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="8"/>
+      <c r="Q89" s="2"/>
+      <c r="R89" s="2"/>
+      <c r="S89" s="2"/>
+      <c r="T89" s="2"/>
+      <c r="U89" s="2"/>
+      <c r="V89" s="4"/>
+      <c r="W89" s="2"/>
+      <c r="X89" s="8">
+        <f>0.7*X88</f>
+        <v>1530784.4440000008</v>
+      </c>
+      <c r="Y89" s="2"/>
+      <c r="Z89" s="2"/>
+      <c r="AA89" s="2"/>
+      <c r="AB89" s="2"/>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="8"/>
+      <c r="Q90" s="2"/>
+      <c r="R90" s="2"/>
+      <c r="S90" s="2"/>
+      <c r="T90" s="2"/>
+      <c r="U90" s="2"/>
+      <c r="V90" s="4"/>
+      <c r="W90" s="2"/>
+      <c r="X90" s="10"/>
+      <c r="Y90" s="2"/>
+      <c r="Z90" s="2"/>
+      <c r="AA90" s="2"/>
+      <c r="AB90" s="2"/>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="8"/>
+      <c r="Q91" s="2"/>
+      <c r="R91" s="2"/>
+      <c r="S91" s="2"/>
+      <c r="T91" s="2"/>
+      <c r="U91" s="2"/>
+      <c r="V91" s="4"/>
+      <c r="W91" s="2"/>
+      <c r="X91" s="10"/>
+      <c r="Y91" s="2"/>
+      <c r="Z91" s="2"/>
+      <c r="AA91" s="2"/>
+      <c r="AB91" s="2"/>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="8"/>
+      <c r="Q92" s="2"/>
+      <c r="R92" s="2"/>
+      <c r="S92" s="2"/>
+      <c r="T92" s="2"/>
+      <c r="U92" s="2"/>
+      <c r="V92" s="4"/>
+      <c r="W92" s="2"/>
+      <c r="X92" s="10"/>
+      <c r="Y92" s="2"/>
+      <c r="Z92" s="2"/>
+      <c r="AA92" s="2"/>
+      <c r="AB92" s="2"/>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="8"/>
+      <c r="Q93" s="2"/>
+      <c r="R93" s="2"/>
+      <c r="S93" s="2"/>
+      <c r="T93" s="2"/>
+      <c r="U93" s="2"/>
+      <c r="V93" s="4"/>
+      <c r="W93" s="2"/>
+      <c r="X93" s="10"/>
+      <c r="Y93" s="2"/>
+      <c r="Z93" s="2"/>
+      <c r="AA93" s="2"/>
+      <c r="AB93" s="2"/>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="8"/>
+      <c r="Q94" s="2"/>
+      <c r="R94" s="2"/>
+      <c r="S94" s="2"/>
+      <c r="T94" s="2"/>
+      <c r="U94" s="2"/>
+      <c r="V94" s="4"/>
+      <c r="W94" s="2"/>
+      <c r="X94" s="10"/>
+      <c r="Y94" s="2"/>
+      <c r="Z94" s="2"/>
+      <c r="AA94" s="2"/>
+      <c r="AB94" s="2"/>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A95" s="2"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="N95" s="2"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="8"/>
+      <c r="Q95" s="2"/>
+      <c r="R95" s="2"/>
+      <c r="S95" s="2"/>
+      <c r="T95" s="2"/>
+      <c r="U95" s="2"/>
+      <c r="V95" s="4"/>
+      <c r="W95" s="2"/>
+      <c r="X95" s="10"/>
+      <c r="Y95" s="2"/>
+      <c r="Z95" s="2"/>
+      <c r="AA95" s="2"/>
+      <c r="AB95" s="2"/>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
+      <c r="N96" s="2"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="8"/>
+      <c r="Q96" s="2"/>
+      <c r="R96" s="2"/>
+      <c r="S96" s="2"/>
+      <c r="T96" s="2"/>
+      <c r="U96" s="2"/>
+      <c r="V96" s="4"/>
+      <c r="W96" s="2"/>
+      <c r="X96" s="10"/>
+      <c r="Y96" s="2"/>
+      <c r="Z96" s="2"/>
+      <c r="AA96" s="2"/>
+      <c r="AB96" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="L1:O1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>